--- a/public/M15_Template.xlsx
+++ b/public/M15_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kyler\OneDrive\桌面\electronic_equiment_rental\Electronic-equipment-rental\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kyler\OneDrive\桌面\mss_ai_department\mss_ai_department\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E1D63A-04CF-48B8-AF64-3A0F083995F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0046EC81-9D47-4C8F-9FA5-131FBCD3627E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="599" activeTab="1" xr2:uid="{99967081-488D-44D6-94DC-7450F6337A9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="110">
   <si>
     <t>Millennium Secondary School</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -728,6 +728,15 @@
   </si>
   <si>
     <t xml:space="preserve"> 年  月  日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">             年           月         日    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        年        月      日    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                      年                      月                  日    </t>
   </si>
 </sst>
 </file>
@@ -2322,23 +2331,56 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -2349,26 +2391,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2376,58 +2430,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2448,8 +2526,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2457,98 +2547,182 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2568,12 +2742,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2586,169 +2754,10 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5026,83 +5035,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="200.15" customHeight="1">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="230" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="177"/>
-      <c r="K1" s="175" t="s">
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="231"/>
+      <c r="F1" s="231"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="232"/>
+      <c r="K1" s="230" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="176"/>
-      <c r="M1" s="176"/>
-      <c r="N1" s="176"/>
-      <c r="O1" s="176"/>
-      <c r="P1" s="176"/>
-      <c r="Q1" s="176"/>
-      <c r="R1" s="176"/>
-      <c r="S1" s="177"/>
+      <c r="L1" s="231"/>
+      <c r="M1" s="231"/>
+      <c r="N1" s="231"/>
+      <c r="O1" s="231"/>
+      <c r="P1" s="231"/>
+      <c r="Q1" s="231"/>
+      <c r="R1" s="231"/>
+      <c r="S1" s="232"/>
     </row>
     <row r="2" spans="1:19" ht="200.15" customHeight="1" thickBot="1">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="233" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="179"/>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="179"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="180"/>
-      <c r="K2" s="178" t="s">
+      <c r="B2" s="234"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="234"/>
+      <c r="I2" s="235"/>
+      <c r="K2" s="233" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="179"/>
-      <c r="M2" s="179"/>
-      <c r="N2" s="179"/>
-      <c r="O2" s="179"/>
-      <c r="P2" s="179"/>
-      <c r="Q2" s="179"/>
-      <c r="R2" s="179"/>
-      <c r="S2" s="180"/>
+      <c r="L2" s="234"/>
+      <c r="M2" s="234"/>
+      <c r="N2" s="234"/>
+      <c r="O2" s="234"/>
+      <c r="P2" s="234"/>
+      <c r="Q2" s="234"/>
+      <c r="R2" s="234"/>
+      <c r="S2" s="235"/>
     </row>
     <row r="3" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A3" s="181">
+      <c r="A3" s="180">
         <v>1</v>
       </c>
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="237" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="186"/>
-      <c r="K3" s="181">
+      <c r="C3" s="238"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="238"/>
+      <c r="H3" s="238"/>
+      <c r="I3" s="239"/>
+      <c r="K3" s="180">
         <v>1</v>
       </c>
-      <c r="L3" s="184" t="s">
+      <c r="L3" s="237" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="185"/>
-      <c r="N3" s="185"/>
-      <c r="O3" s="185"/>
-      <c r="P3" s="185"/>
-      <c r="Q3" s="185"/>
-      <c r="R3" s="185"/>
-      <c r="S3" s="186"/>
+      <c r="M3" s="238"/>
+      <c r="N3" s="238"/>
+      <c r="O3" s="238"/>
+      <c r="P3" s="238"/>
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="239"/>
     </row>
     <row r="4" spans="1:19" s="12" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A4" s="182"/>
+      <c r="A4" s="181"/>
       <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
@@ -5119,7 +5128,7 @@
         <v>79</v>
       </c>
       <c r="I4" s="11"/>
-      <c r="K4" s="182"/>
+      <c r="K4" s="181"/>
       <c r="L4" s="8" t="s">
         <v>19</v>
       </c>
@@ -5138,7 +5147,7 @@
       <c r="S4" s="11"/>
     </row>
     <row r="5" spans="1:19" s="12" customFormat="1" ht="222" customHeight="1" thickBot="1">
-      <c r="A5" s="183"/>
+      <c r="A5" s="236"/>
       <c r="B5" s="13" t="s">
         <v>17</v>
       </c>
@@ -5155,7 +5164,7 @@
         <v>80</v>
       </c>
       <c r="I5" s="16"/>
-      <c r="K5" s="183"/>
+      <c r="K5" s="236"/>
       <c r="L5" s="13" t="s">
         <v>17</v>
       </c>
@@ -5174,7 +5183,7 @@
       <c r="S5" s="16"/>
     </row>
     <row r="6" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A6" s="218">
+      <c r="A6" s="204">
         <v>2</v>
       </c>
       <c r="B6" s="17" t="s">
@@ -5187,7 +5196,7 @@
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
       <c r="I6" s="19"/>
-      <c r="K6" s="218">
+      <c r="K6" s="204">
         <v>2</v>
       </c>
       <c r="L6" s="17" t="s">
@@ -5202,43 +5211,43 @@
       <c r="S6" s="19"/>
     </row>
     <row r="7" spans="1:19" s="12" customFormat="1" ht="289.5" customHeight="1">
-      <c r="A7" s="219"/>
-      <c r="B7" s="222" t="s">
+      <c r="A7" s="205"/>
+      <c r="B7" s="214" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="223"/>
-      <c r="D7" s="223"/>
-      <c r="E7" s="223"/>
+      <c r="C7" s="215"/>
+      <c r="D7" s="215"/>
+      <c r="E7" s="215"/>
       <c r="F7" s="90" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="H7" s="187" t="s">
+      <c r="H7" s="216" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="188"/>
-      <c r="K7" s="219"/>
-      <c r="L7" s="222" t="s">
+      <c r="I7" s="217"/>
+      <c r="K7" s="205"/>
+      <c r="L7" s="214" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="223"/>
-      <c r="N7" s="223"/>
-      <c r="O7" s="223"/>
+      <c r="M7" s="215"/>
+      <c r="N7" s="215"/>
+      <c r="O7" s="215"/>
       <c r="P7" s="90" t="s">
         <v>82</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="R7" s="187" t="s">
+      <c r="R7" s="216" t="s">
         <v>85</v>
       </c>
-      <c r="S7" s="188"/>
+      <c r="S7" s="217"/>
     </row>
     <row r="8" spans="1:19" s="12" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A8" s="219"/>
+      <c r="A8" s="205"/>
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
@@ -5255,7 +5264,7 @@
         <v>36</v>
       </c>
       <c r="I8" s="11"/>
-      <c r="K8" s="219"/>
+      <c r="K8" s="205"/>
       <c r="L8" s="8" t="s">
         <v>13</v>
       </c>
@@ -5274,7 +5283,7 @@
       <c r="S8" s="11"/>
     </row>
     <row r="9" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A9" s="219"/>
+      <c r="A9" s="205"/>
       <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
@@ -5291,7 +5300,7 @@
       <c r="I9" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="219"/>
+      <c r="K9" s="205"/>
       <c r="L9" s="8" t="s">
         <v>12</v>
       </c>
@@ -5310,7 +5319,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A10" s="219"/>
+      <c r="A10" s="205"/>
       <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
@@ -5327,7 +5336,7 @@
         <v>1800</v>
       </c>
       <c r="I10" s="33"/>
-      <c r="K10" s="219"/>
+      <c r="K10" s="205"/>
       <c r="L10" s="28" t="s">
         <v>8</v>
       </c>
@@ -5346,8 +5355,8 @@
       <c r="S10" s="33"/>
     </row>
     <row r="11" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A11" s="219"/>
-      <c r="B11" s="212" t="s">
+      <c r="A11" s="205"/>
+      <c r="B11" s="198" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="34" t="s">
@@ -5359,8 +5368,8 @@
       <c r="G11" s="36"/>
       <c r="H11" s="36"/>
       <c r="I11" s="37"/>
-      <c r="K11" s="219"/>
-      <c r="L11" s="212" t="s">
+      <c r="K11" s="205"/>
+      <c r="L11" s="198" t="s">
         <v>7</v>
       </c>
       <c r="M11" s="34" t="s">
@@ -5374,8 +5383,8 @@
       <c r="S11" s="37"/>
     </row>
     <row r="12" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A12" s="219"/>
-      <c r="B12" s="213"/>
+      <c r="A12" s="205"/>
+      <c r="B12" s="199"/>
       <c r="C12" s="34" t="s">
         <v>30</v>
       </c>
@@ -5385,8 +5394,8 @@
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
       <c r="I12" s="33"/>
-      <c r="K12" s="219"/>
-      <c r="L12" s="213"/>
+      <c r="K12" s="205"/>
+      <c r="L12" s="199"/>
       <c r="M12" s="34" t="s">
         <v>30</v>
       </c>
@@ -5398,60 +5407,60 @@
       <c r="S12" s="33"/>
     </row>
     <row r="13" spans="1:19" s="27" customFormat="1" ht="199.5" customHeight="1">
-      <c r="A13" s="219"/>
-      <c r="B13" s="214"/>
-      <c r="C13" s="215" t="s">
+      <c r="A13" s="205"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="201" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="216"/>
-      <c r="E13" s="216"/>
-      <c r="F13" s="217"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="202"/>
+      <c r="F13" s="203"/>
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
       <c r="I13" s="33"/>
-      <c r="K13" s="219"/>
-      <c r="L13" s="214"/>
-      <c r="M13" s="215" t="s">
+      <c r="K13" s="205"/>
+      <c r="L13" s="200"/>
+      <c r="M13" s="201" t="s">
         <v>6</v>
       </c>
-      <c r="N13" s="216"/>
-      <c r="O13" s="216"/>
-      <c r="P13" s="217"/>
+      <c r="N13" s="202"/>
+      <c r="O13" s="202"/>
+      <c r="P13" s="203"/>
       <c r="Q13" s="32"/>
       <c r="R13" s="32"/>
       <c r="S13" s="33"/>
     </row>
     <row r="14" spans="1:19" s="27" customFormat="1" ht="250" customHeight="1">
-      <c r="A14" s="219"/>
-      <c r="B14" s="212" t="s">
+      <c r="A14" s="205"/>
+      <c r="B14" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="197" t="s">
+      <c r="C14" s="211" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="198"/>
-      <c r="E14" s="198"/>
-      <c r="F14" s="199"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
+      <c r="F14" s="213"/>
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
       <c r="I14" s="33"/>
-      <c r="K14" s="219"/>
-      <c r="L14" s="212" t="s">
+      <c r="K14" s="205"/>
+      <c r="L14" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="197" t="s">
+      <c r="M14" s="211" t="s">
         <v>68</v>
       </c>
-      <c r="N14" s="198"/>
-      <c r="O14" s="198"/>
-      <c r="P14" s="199"/>
+      <c r="N14" s="212"/>
+      <c r="O14" s="212"/>
+      <c r="P14" s="213"/>
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="33"/>
     </row>
     <row r="15" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A15" s="219"/>
-      <c r="B15" s="213"/>
+      <c r="A15" s="205"/>
+      <c r="B15" s="199"/>
       <c r="C15" s="34" t="s">
         <v>31</v>
       </c>
@@ -5461,8 +5470,8 @@
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
-      <c r="K15" s="219"/>
-      <c r="L15" s="213"/>
+      <c r="K15" s="205"/>
+      <c r="L15" s="199"/>
       <c r="M15" s="34" t="s">
         <v>31</v>
       </c>
@@ -5474,8 +5483,8 @@
       <c r="S15" s="33"/>
     </row>
     <row r="16" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A16" s="219"/>
-      <c r="B16" s="213"/>
+      <c r="A16" s="205"/>
+      <c r="B16" s="199"/>
       <c r="C16" s="34" t="s">
         <v>32</v>
       </c>
@@ -5485,8 +5494,8 @@
       <c r="G16" s="38"/>
       <c r="H16" s="77"/>
       <c r="I16" s="78"/>
-      <c r="K16" s="219"/>
-      <c r="L16" s="213"/>
+      <c r="K16" s="205"/>
+      <c r="L16" s="199"/>
       <c r="M16" s="34" t="s">
         <v>32</v>
       </c>
@@ -5498,8 +5507,8 @@
       <c r="S16" s="78"/>
     </row>
     <row r="17" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A17" s="219"/>
-      <c r="B17" s="213"/>
+      <c r="A17" s="205"/>
+      <c r="B17" s="199"/>
       <c r="C17" s="34" t="s">
         <v>37</v>
       </c>
@@ -5509,8 +5518,8 @@
       <c r="G17" s="38"/>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="K17" s="219"/>
-      <c r="L17" s="213"/>
+      <c r="K17" s="205"/>
+      <c r="L17" s="199"/>
       <c r="M17" s="34" t="s">
         <v>37</v>
       </c>
@@ -5522,32 +5531,32 @@
       <c r="S17" s="40"/>
     </row>
     <row r="18" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A18" s="219"/>
-      <c r="B18" s="213"/>
-      <c r="C18" s="194" t="s">
+      <c r="A18" s="205"/>
+      <c r="B18" s="199"/>
+      <c r="C18" s="208" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="195"/>
-      <c r="E18" s="195"/>
-      <c r="F18" s="196"/>
+      <c r="D18" s="209"/>
+      <c r="E18" s="209"/>
+      <c r="F18" s="210"/>
       <c r="G18" s="41"/>
       <c r="H18" s="41"/>
       <c r="I18" s="42"/>
-      <c r="K18" s="219"/>
-      <c r="L18" s="213"/>
-      <c r="M18" s="194" t="s">
+      <c r="K18" s="205"/>
+      <c r="L18" s="199"/>
+      <c r="M18" s="208" t="s">
         <v>38</v>
       </c>
-      <c r="N18" s="195"/>
-      <c r="O18" s="195"/>
-      <c r="P18" s="196"/>
+      <c r="N18" s="209"/>
+      <c r="O18" s="209"/>
+      <c r="P18" s="210"/>
       <c r="Q18" s="41"/>
       <c r="R18" s="41"/>
       <c r="S18" s="42"/>
     </row>
     <row r="19" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A19" s="219"/>
-      <c r="B19" s="213"/>
+      <c r="A19" s="205"/>
+      <c r="B19" s="199"/>
       <c r="C19" s="43" t="s">
         <v>4</v>
       </c>
@@ -5557,8 +5566,8 @@
       <c r="G19" s="44"/>
       <c r="H19" s="44"/>
       <c r="I19" s="40"/>
-      <c r="K19" s="219"/>
-      <c r="L19" s="213"/>
+      <c r="K19" s="205"/>
+      <c r="L19" s="199"/>
       <c r="M19" s="43" t="s">
         <v>4</v>
       </c>
@@ -5570,8 +5579,8 @@
       <c r="S19" s="40"/>
     </row>
     <row r="20" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A20" s="219"/>
-      <c r="B20" s="213"/>
+      <c r="A20" s="205"/>
+      <c r="B20" s="199"/>
       <c r="C20" s="34" t="s">
         <v>33</v>
       </c>
@@ -5581,8 +5590,8 @@
       <c r="G20" s="45"/>
       <c r="H20" s="45"/>
       <c r="I20" s="46"/>
-      <c r="K20" s="219"/>
-      <c r="L20" s="213"/>
+      <c r="K20" s="205"/>
+      <c r="L20" s="199"/>
       <c r="M20" s="34" t="s">
         <v>33</v>
       </c>
@@ -5594,8 +5603,8 @@
       <c r="S20" s="46"/>
     </row>
     <row r="21" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1" thickBot="1">
-      <c r="A21" s="220"/>
-      <c r="B21" s="221"/>
+      <c r="A21" s="206"/>
+      <c r="B21" s="207"/>
       <c r="C21" s="34" t="s">
         <v>34</v>
       </c>
@@ -5605,8 +5614,8 @@
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
       <c r="I21" s="47"/>
-      <c r="K21" s="220"/>
-      <c r="L21" s="221"/>
+      <c r="K21" s="206"/>
+      <c r="L21" s="207"/>
       <c r="M21" s="34" t="s">
         <v>34</v>
       </c>
@@ -5618,85 +5627,85 @@
       <c r="S21" s="47"/>
     </row>
     <row r="22" spans="1:19" s="7" customFormat="1" ht="132" customHeight="1">
-      <c r="A22" s="181">
+      <c r="A22" s="180">
         <v>3</v>
       </c>
-      <c r="B22" s="224" t="s">
+      <c r="B22" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="225"/>
-      <c r="D22" s="225"/>
-      <c r="E22" s="225"/>
-      <c r="F22" s="225"/>
-      <c r="G22" s="225"/>
-      <c r="H22" s="225"/>
-      <c r="I22" s="226"/>
-      <c r="K22" s="181">
+      <c r="C22" s="183"/>
+      <c r="D22" s="183"/>
+      <c r="E22" s="183"/>
+      <c r="F22" s="183"/>
+      <c r="G22" s="183"/>
+      <c r="H22" s="183"/>
+      <c r="I22" s="184"/>
+      <c r="K22" s="180">
         <v>3</v>
       </c>
-      <c r="L22" s="224" t="s">
+      <c r="L22" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="225"/>
-      <c r="N22" s="225"/>
-      <c r="O22" s="225"/>
-      <c r="P22" s="225"/>
-      <c r="Q22" s="225"/>
-      <c r="R22" s="225"/>
-      <c r="S22" s="226"/>
+      <c r="M22" s="183"/>
+      <c r="N22" s="183"/>
+      <c r="O22" s="183"/>
+      <c r="P22" s="183"/>
+      <c r="Q22" s="183"/>
+      <c r="R22" s="183"/>
+      <c r="S22" s="184"/>
     </row>
     <row r="23" spans="1:19" s="27" customFormat="1" ht="274.5" customHeight="1">
-      <c r="A23" s="182"/>
-      <c r="B23" s="227" t="s">
+      <c r="A23" s="181"/>
+      <c r="B23" s="185" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="228"/>
-      <c r="D23" s="206" t="s">
+      <c r="C23" s="186"/>
+      <c r="D23" s="187" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="229"/>
-      <c r="F23" s="228"/>
-      <c r="G23" s="206" t="s">
+      <c r="E23" s="188"/>
+      <c r="F23" s="186"/>
+      <c r="G23" s="187" t="s">
         <v>55</v>
       </c>
-      <c r="H23" s="207"/>
+      <c r="H23" s="189"/>
       <c r="I23" s="48"/>
-      <c r="K23" s="182"/>
-      <c r="L23" s="227" t="s">
+      <c r="K23" s="181"/>
+      <c r="L23" s="185" t="s">
         <v>58</v>
       </c>
-      <c r="M23" s="228"/>
-      <c r="N23" s="206" t="s">
+      <c r="M23" s="186"/>
+      <c r="N23" s="187" t="s">
         <v>63</v>
       </c>
-      <c r="O23" s="229"/>
-      <c r="P23" s="228"/>
-      <c r="Q23" s="206" t="s">
+      <c r="O23" s="188"/>
+      <c r="P23" s="186"/>
+      <c r="Q23" s="187" t="s">
         <v>56</v>
       </c>
-      <c r="R23" s="207"/>
+      <c r="R23" s="189"/>
       <c r="S23" s="48"/>
     </row>
     <row r="24" spans="1:19" s="27" customFormat="1" ht="267" customHeight="1">
-      <c r="A24" s="182"/>
+      <c r="A24" s="181"/>
       <c r="B24" s="89"/>
       <c r="C24" s="88"/>
-      <c r="D24" s="232" t="s">
+      <c r="D24" s="195" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="233"/>
-      <c r="F24" s="234"/>
+      <c r="E24" s="196"/>
+      <c r="F24" s="197"/>
       <c r="G24" s="87"/>
       <c r="H24" s="49" t="s">
         <v>39</v>
       </c>
       <c r="I24" s="48"/>
-      <c r="K24" s="182"/>
+      <c r="K24" s="181"/>
       <c r="L24" s="89"/>
       <c r="M24" s="79"/>
-      <c r="N24" s="232"/>
-      <c r="O24" s="233"/>
-      <c r="P24" s="234"/>
+      <c r="N24" s="195"/>
+      <c r="O24" s="196"/>
+      <c r="P24" s="197"/>
       <c r="Q24" s="87"/>
       <c r="R24" s="49" t="s">
         <v>39</v>
@@ -5704,65 +5713,65 @@
       <c r="S24" s="48"/>
     </row>
     <row r="25" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A25" s="182"/>
+      <c r="A25" s="181"/>
       <c r="B25" s="80"/>
       <c r="C25" s="81"/>
       <c r="D25" s="82"/>
       <c r="E25" s="83"/>
       <c r="F25" s="81"/>
       <c r="G25" s="96"/>
-      <c r="H25" s="189" t="s">
+      <c r="H25" s="224" t="s">
         <v>67</v>
       </c>
-      <c r="I25" s="190"/>
-      <c r="K25" s="182"/>
+      <c r="I25" s="225"/>
+      <c r="K25" s="181"/>
       <c r="L25" s="51"/>
       <c r="M25" s="91"/>
       <c r="N25" s="82"/>
       <c r="O25" s="83"/>
       <c r="P25" s="81"/>
       <c r="Q25" s="96"/>
-      <c r="R25" s="189" t="s">
+      <c r="R25" s="224" t="s">
         <v>2</v>
       </c>
-      <c r="S25" s="190"/>
+      <c r="S25" s="225"/>
     </row>
     <row r="26" spans="1:19" s="27" customFormat="1" ht="237" customHeight="1" thickBot="1">
-      <c r="A26" s="182"/>
-      <c r="B26" s="230" t="s">
+      <c r="A26" s="181"/>
+      <c r="B26" s="193" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="231"/>
-      <c r="D26" s="191" t="s">
+      <c r="C26" s="194"/>
+      <c r="D26" s="190" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="192"/>
-      <c r="F26" s="193"/>
+      <c r="E26" s="191"/>
+      <c r="F26" s="192"/>
       <c r="G26" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="208" t="s">
+      <c r="H26" s="226" t="s">
         <v>71</v>
       </c>
-      <c r="I26" s="209"/>
+      <c r="I26" s="227"/>
       <c r="J26" s="93"/>
-      <c r="K26" s="182"/>
-      <c r="L26" s="230" t="s">
+      <c r="K26" s="181"/>
+      <c r="L26" s="193" t="s">
         <v>69</v>
       </c>
-      <c r="M26" s="231"/>
-      <c r="N26" s="191" t="s">
+      <c r="M26" s="194"/>
+      <c r="N26" s="190" t="s">
         <v>70</v>
       </c>
-      <c r="O26" s="192"/>
-      <c r="P26" s="193"/>
+      <c r="O26" s="191"/>
+      <c r="P26" s="192"/>
       <c r="Q26" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="R26" s="210" t="s">
+      <c r="R26" s="228" t="s">
         <v>71</v>
       </c>
-      <c r="S26" s="211"/>
+      <c r="S26" s="229"/>
     </row>
     <row r="27" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
       <c r="A27" s="50" t="s">
@@ -5786,10 +5795,10 @@
       <c r="O27" s="92"/>
       <c r="P27" s="92"/>
       <c r="Q27" s="92"/>
-      <c r="R27" s="200" t="s">
+      <c r="R27" s="218" t="s">
         <v>40</v>
       </c>
-      <c r="S27" s="201"/>
+      <c r="S27" s="219"/>
     </row>
     <row r="28" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
       <c r="A28" s="51"/>
@@ -5801,8 +5810,8 @@
       <c r="M28" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="R28" s="202"/>
-      <c r="S28" s="203"/>
+      <c r="R28" s="220"/>
+      <c r="S28" s="221"/>
     </row>
     <row r="29" spans="1:19" ht="79.5" customHeight="1" thickBot="1">
       <c r="A29" s="52"/>
@@ -5822,8 +5831,8 @@
       <c r="O29" s="53"/>
       <c r="P29" s="53"/>
       <c r="Q29" s="53"/>
-      <c r="R29" s="204"/>
-      <c r="S29" s="205"/>
+      <c r="R29" s="222"/>
+      <c r="S29" s="223"/>
     </row>
     <row r="50" spans="13:13">
       <c r="M50" s="94"/>
@@ -5833,6 +5842,37 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="M14:P14"/>
+    <mergeCell ref="R27:S29"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="A6:A21"/>
+    <mergeCell ref="K6:K21"/>
+    <mergeCell ref="B14:B21"/>
+    <mergeCell ref="L14:L21"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="L7:O7"/>
     <mergeCell ref="A22:A26"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="K22:K26"/>
@@ -5847,37 +5887,6 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="N23:P23"/>
     <mergeCell ref="N24:P24"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="A6:A21"/>
-    <mergeCell ref="K6:K21"/>
-    <mergeCell ref="B14:B21"/>
-    <mergeCell ref="L14:L21"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="R27:S29"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="M18:P18"/>
-    <mergeCell ref="M14:P14"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:S3"/>
-    <mergeCell ref="B3:I3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5915,83 +5924,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21.5">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="101"/>
-      <c r="K1" s="99" t="s">
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="173"/>
+      <c r="K1" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="100"/>
-      <c r="S1" s="101"/>
+      <c r="L1" s="172"/>
+      <c r="M1" s="172"/>
+      <c r="N1" s="172"/>
+      <c r="O1" s="172"/>
+      <c r="P1" s="172"/>
+      <c r="Q1" s="172"/>
+      <c r="R1" s="172"/>
+      <c r="S1" s="173"/>
     </row>
     <row r="2" spans="1:19" ht="22" thickBot="1">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="174" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="104"/>
-      <c r="K2" s="102" t="s">
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="176"/>
+      <c r="K2" s="174" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="103"/>
-      <c r="S2" s="104"/>
+      <c r="L2" s="175"/>
+      <c r="M2" s="175"/>
+      <c r="N2" s="175"/>
+      <c r="O2" s="175"/>
+      <c r="P2" s="175"/>
+      <c r="Q2" s="175"/>
+      <c r="R2" s="175"/>
+      <c r="S2" s="176"/>
     </row>
     <row r="3" spans="1:19" ht="25" customHeight="1">
-      <c r="A3" s="105">
+      <c r="A3" s="116">
         <v>1</v>
       </c>
-      <c r="B3" s="108" t="s">
+      <c r="B3" s="177" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="110"/>
-      <c r="K3" s="105">
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="179"/>
+      <c r="K3" s="116">
         <v>1</v>
       </c>
-      <c r="L3" s="108" t="s">
+      <c r="L3" s="177" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="109"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="109"/>
-      <c r="P3" s="109"/>
-      <c r="Q3" s="109"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="110"/>
+      <c r="M3" s="178"/>
+      <c r="N3" s="178"/>
+      <c r="O3" s="178"/>
+      <c r="P3" s="178"/>
+      <c r="Q3" s="178"/>
+      <c r="R3" s="178"/>
+      <c r="S3" s="179"/>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
-      <c r="A4" s="106"/>
+      <c r="A4" s="117"/>
       <c r="B4" s="68" t="s">
         <v>44</v>
       </c>
@@ -6004,7 +6013,7 @@
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="5"/>
-      <c r="K4" s="106"/>
+      <c r="K4" s="117"/>
       <c r="L4" s="68" t="s">
         <v>44</v>
       </c>
@@ -6025,7 +6034,7 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1" thickBot="1">
-      <c r="A5" s="107"/>
+      <c r="A5" s="118"/>
       <c r="B5" s="70" t="s">
         <v>45</v>
       </c>
@@ -6038,7 +6047,7 @@
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="3"/>
-      <c r="K5" s="107"/>
+      <c r="K5" s="118"/>
       <c r="L5" s="70" t="s">
         <v>45</v>
       </c>
@@ -6059,7 +6068,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
-      <c r="A6" s="141">
+      <c r="A6" s="106">
         <v>2</v>
       </c>
       <c r="B6" s="64" t="s">
@@ -6072,7 +6081,7 @@
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
       <c r="I6" s="65"/>
-      <c r="K6" s="141">
+      <c r="K6" s="106">
         <v>2</v>
       </c>
       <c r="L6" s="64" t="s">
@@ -6087,7 +6096,7 @@
       <c r="S6" s="65"/>
     </row>
     <row r="7" spans="1:19" ht="32.25" customHeight="1">
-      <c r="A7" s="141"/>
+      <c r="A7" s="106"/>
       <c r="B7" s="68" t="s">
         <v>48</v>
       </c>
@@ -6095,14 +6104,14 @@
       <c r="D7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="142"/>
-      <c r="F7" s="142"/>
-      <c r="G7" s="142"/>
-      <c r="H7" s="142"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
       <c r="I7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="141"/>
+      <c r="K7" s="106"/>
       <c r="L7" s="68" t="s">
         <v>48</v>
       </c>
@@ -6110,19 +6119,19 @@
       <c r="N7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="142" t="str">
+      <c r="O7" s="169" t="str">
         <f>IF(E7="","",E7)</f>
         <v/>
       </c>
-      <c r="P7" s="142"/>
-      <c r="Q7" s="142"/>
-      <c r="R7" s="142"/>
+      <c r="P7" s="169"/>
+      <c r="Q7" s="169"/>
+      <c r="R7" s="169"/>
       <c r="S7" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="37.5" customHeight="1">
-      <c r="A8" s="141"/>
+      <c r="A8" s="106"/>
       <c r="B8" s="68" t="s">
         <v>51</v>
       </c>
@@ -6133,7 +6142,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
       <c r="I8" s="5"/>
-      <c r="K8" s="141"/>
+      <c r="K8" s="106"/>
       <c r="L8" s="68" t="s">
         <v>51</v>
       </c>
@@ -6149,44 +6158,44 @@
       <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" ht="25" customHeight="1">
-      <c r="A9" s="141"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="68"/>
-      <c r="C9" s="143" t="s">
+      <c r="C9" s="170" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="114"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
       <c r="G9" s="55"/>
-      <c r="H9" s="144" t="s">
+      <c r="H9" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="145"/>
-      <c r="K9" s="141"/>
+      <c r="I9" s="108"/>
+      <c r="K9" s="106"/>
       <c r="L9" s="68"/>
-      <c r="M9" s="143" t="s">
+      <c r="M9" s="170" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="114"/>
-      <c r="O9" s="114"/>
-      <c r="P9" s="114"/>
+      <c r="N9" s="112"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="112"/>
       <c r="Q9" s="55"/>
-      <c r="R9" s="144" t="s">
+      <c r="R9" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="S9" s="145"/>
+      <c r="S9" s="108"/>
     </row>
     <row r="10" spans="1:19" ht="25" customHeight="1">
-      <c r="A10" s="141"/>
+      <c r="A10" s="106"/>
       <c r="B10" s="56"/>
-      <c r="C10" s="111" t="s">
+      <c r="C10" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113" t="s">
+      <c r="D10" s="110"/>
+      <c r="E10" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="114"/>
+      <c r="F10" s="112"/>
       <c r="G10" s="55"/>
       <c r="H10" s="57" t="s">
         <v>23</v>
@@ -6194,16 +6203,16 @@
       <c r="I10" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="141"/>
+      <c r="K10" s="106"/>
       <c r="L10" s="56"/>
-      <c r="M10" s="111" t="s">
+      <c r="M10" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="112"/>
-      <c r="O10" s="113" t="s">
+      <c r="N10" s="110"/>
+      <c r="O10" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="114"/>
+      <c r="P10" s="112"/>
       <c r="Q10" s="55"/>
       <c r="R10" s="57" t="s">
         <v>23</v>
@@ -6213,366 +6222,366 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="28" customHeight="1">
-      <c r="A11" s="141"/>
-      <c r="B11" s="115">
+      <c r="A11" s="106"/>
+      <c r="B11" s="130">
         <v>1</v>
       </c>
-      <c r="C11" s="118" t="s">
+      <c r="C11" s="133" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="237"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="125"/>
+      <c r="D11" s="164"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="140"/>
       <c r="G11" s="59"/>
-      <c r="H11" s="130" t="s">
+      <c r="H11" s="145" t="s">
         <v>106</v>
       </c>
-      <c r="I11" s="133"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="115">
+      <c r="I11" s="151"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="130">
         <v>1</v>
       </c>
-      <c r="M11" s="118" t="str">
+      <c r="M11" s="133" t="str">
         <f>C11</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="N11" s="119"/>
-      <c r="O11" s="124" t="str">
+      <c r="N11" s="134"/>
+      <c r="O11" s="155" t="str">
         <f>IF(E11="","",E11)</f>
         <v/>
       </c>
-      <c r="P11" s="136"/>
+      <c r="P11" s="159"/>
       <c r="Q11" s="59"/>
-      <c r="R11" s="130" t="str">
+      <c r="R11" s="145" t="str">
         <f>H11</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="S11" s="133" t="str">
+      <c r="S11" s="151" t="str">
         <f>IF(I11="","",I11)</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:19" ht="28" customHeight="1">
-      <c r="A12" s="141"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="238"/>
-      <c r="D12" s="239"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="127"/>
+      <c r="A12" s="106"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="165"/>
+      <c r="D12" s="166"/>
+      <c r="E12" s="141"/>
+      <c r="F12" s="142"/>
       <c r="G12" s="61"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="134"/>
-      <c r="K12" s="141"/>
-      <c r="L12" s="116"/>
-      <c r="M12" s="120"/>
-      <c r="N12" s="121"/>
-      <c r="O12" s="137"/>
-      <c r="P12" s="138"/>
+      <c r="H12" s="146"/>
+      <c r="I12" s="149"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="135"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="160"/>
+      <c r="P12" s="161"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="131"/>
-      <c r="S12" s="146"/>
+      <c r="R12" s="146"/>
+      <c r="S12" s="152"/>
     </row>
     <row r="13" spans="1:19" ht="28" customHeight="1">
-      <c r="A13" s="141"/>
-      <c r="B13" s="117"/>
-      <c r="C13" s="240"/>
-      <c r="D13" s="241"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="129"/>
+      <c r="A13" s="106"/>
+      <c r="B13" s="154"/>
+      <c r="C13" s="167"/>
+      <c r="D13" s="168"/>
+      <c r="E13" s="156"/>
+      <c r="F13" s="157"/>
       <c r="G13" s="60"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="135"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="117"/>
-      <c r="M13" s="122"/>
-      <c r="N13" s="123"/>
-      <c r="O13" s="139"/>
-      <c r="P13" s="140"/>
+      <c r="H13" s="147"/>
+      <c r="I13" s="158"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="154"/>
+      <c r="M13" s="137"/>
+      <c r="N13" s="138"/>
+      <c r="O13" s="162"/>
+      <c r="P13" s="163"/>
       <c r="Q13" s="60"/>
-      <c r="R13" s="132"/>
-      <c r="S13" s="147"/>
+      <c r="R13" s="147"/>
+      <c r="S13" s="153"/>
     </row>
     <row r="14" spans="1:19" ht="28" customHeight="1">
-      <c r="A14" s="141"/>
-      <c r="B14" s="115">
+      <c r="A14" s="106"/>
+      <c r="B14" s="130">
         <v>2</v>
       </c>
-      <c r="C14" s="118" t="s">
+      <c r="C14" s="133" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="119"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="125"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="155"/>
+      <c r="F14" s="140"/>
       <c r="G14" s="59"/>
-      <c r="H14" s="130" t="s">
+      <c r="H14" s="145" t="s">
         <v>106</v>
       </c>
-      <c r="I14" s="133"/>
-      <c r="K14" s="141"/>
-      <c r="L14" s="115">
+      <c r="I14" s="151"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="130">
         <v>2</v>
       </c>
-      <c r="M14" s="118" t="str">
+      <c r="M14" s="133" t="str">
         <f>C14</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="N14" s="119"/>
-      <c r="O14" s="124" t="str">
+      <c r="N14" s="134"/>
+      <c r="O14" s="155" t="str">
         <f>IF(E14="","",E14)</f>
         <v/>
       </c>
-      <c r="P14" s="136"/>
+      <c r="P14" s="159"/>
       <c r="Q14" s="59"/>
-      <c r="R14" s="130" t="str">
+      <c r="R14" s="145" t="str">
         <f>H14</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="S14" s="133" t="str">
+      <c r="S14" s="151" t="str">
         <f>IF(I14="","",I14)</f>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:19" ht="28" customHeight="1">
-      <c r="A15" s="141"/>
-      <c r="B15" s="116"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="127"/>
+      <c r="A15" s="106"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="142"/>
       <c r="G15" s="61"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="134"/>
-      <c r="K15" s="141"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="137"/>
-      <c r="P15" s="138"/>
+      <c r="H15" s="146"/>
+      <c r="I15" s="149"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="131"/>
+      <c r="M15" s="135"/>
+      <c r="N15" s="136"/>
+      <c r="O15" s="160"/>
+      <c r="P15" s="161"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="131"/>
-      <c r="S15" s="146"/>
+      <c r="R15" s="146"/>
+      <c r="S15" s="152"/>
     </row>
     <row r="16" spans="1:19" ht="28" customHeight="1">
-      <c r="A16" s="141"/>
-      <c r="B16" s="117"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="129"/>
+      <c r="A16" s="106"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="156"/>
+      <c r="F16" s="157"/>
       <c r="G16" s="60"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="135"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="122"/>
-      <c r="N16" s="123"/>
-      <c r="O16" s="139"/>
-      <c r="P16" s="140"/>
+      <c r="H16" s="147"/>
+      <c r="I16" s="158"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="154"/>
+      <c r="M16" s="137"/>
+      <c r="N16" s="138"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="163"/>
       <c r="Q16" s="60"/>
-      <c r="R16" s="132"/>
-      <c r="S16" s="147"/>
+      <c r="R16" s="147"/>
+      <c r="S16" s="153"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1">
-      <c r="A17" s="141"/>
-      <c r="B17" s="115">
+      <c r="A17" s="106"/>
+      <c r="B17" s="130">
         <v>3</v>
       </c>
-      <c r="C17" s="118" t="s">
+      <c r="C17" s="133" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="119"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="125"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="140"/>
       <c r="G17" s="59"/>
-      <c r="H17" s="130" t="s">
+      <c r="H17" s="145" t="s">
         <v>106</v>
       </c>
-      <c r="I17" s="133"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="115">
+      <c r="I17" s="151"/>
+      <c r="K17" s="106"/>
+      <c r="L17" s="130">
         <v>3</v>
       </c>
-      <c r="M17" s="118" t="str">
+      <c r="M17" s="133" t="str">
         <f>C17</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="N17" s="119"/>
-      <c r="O17" s="149" t="str">
+      <c r="N17" s="134"/>
+      <c r="O17" s="139" t="str">
         <f>IF(E17="","",E17)</f>
         <v/>
       </c>
-      <c r="P17" s="125"/>
+      <c r="P17" s="140"/>
       <c r="Q17" s="59"/>
-      <c r="R17" s="130" t="str">
+      <c r="R17" s="145" t="str">
         <f>H17</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="S17" s="158" t="str">
+      <c r="S17" s="148" t="str">
         <f>IF(I17="","",I17)</f>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1">
-      <c r="A18" s="141"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="120"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="126"/>
-      <c r="F18" s="127"/>
+      <c r="A18" s="106"/>
+      <c r="B18" s="131"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="136"/>
+      <c r="E18" s="141"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="61"/>
-      <c r="H18" s="131"/>
-      <c r="I18" s="134"/>
-      <c r="K18" s="141"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="126"/>
-      <c r="P18" s="127"/>
+      <c r="H18" s="146"/>
+      <c r="I18" s="149"/>
+      <c r="K18" s="106"/>
+      <c r="L18" s="131"/>
+      <c r="M18" s="135"/>
+      <c r="N18" s="136"/>
+      <c r="O18" s="141"/>
+      <c r="P18" s="142"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="131"/>
-      <c r="S18" s="134"/>
+      <c r="R18" s="146"/>
+      <c r="S18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" thickBot="1">
-      <c r="A19" s="141"/>
-      <c r="B19" s="148"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="151"/>
+      <c r="A19" s="106"/>
+      <c r="B19" s="132"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="144"/>
       <c r="G19" s="62"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="152"/>
-      <c r="K19" s="141"/>
-      <c r="L19" s="148"/>
-      <c r="M19" s="122"/>
-      <c r="N19" s="123"/>
-      <c r="O19" s="150"/>
-      <c r="P19" s="151"/>
+      <c r="H19" s="147"/>
+      <c r="I19" s="150"/>
+      <c r="K19" s="106"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="137"/>
+      <c r="N19" s="138"/>
+      <c r="O19" s="143"/>
+      <c r="P19" s="144"/>
       <c r="Q19" s="62"/>
-      <c r="R19" s="132"/>
-      <c r="S19" s="152"/>
+      <c r="R19" s="147"/>
+      <c r="S19" s="150"/>
     </row>
     <row r="20" spans="1:20" ht="20.25" customHeight="1">
-      <c r="A20" s="105">
+      <c r="A20" s="116">
         <v>3</v>
       </c>
-      <c r="B20" s="172" t="s">
+      <c r="B20" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="173"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="173"/>
-      <c r="I20" s="174"/>
-      <c r="K20" s="105">
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="121"/>
+      <c r="K20" s="116">
         <v>3</v>
       </c>
-      <c r="L20" s="172" t="s">
+      <c r="L20" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="M20" s="173"/>
-      <c r="N20" s="173"/>
-      <c r="O20" s="173"/>
-      <c r="P20" s="173"/>
-      <c r="Q20" s="173"/>
-      <c r="R20" s="173"/>
-      <c r="S20" s="174"/>
+      <c r="M20" s="120"/>
+      <c r="N20" s="120"/>
+      <c r="O20" s="120"/>
+      <c r="P20" s="120"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="120"/>
+      <c r="S20" s="121"/>
     </row>
     <row r="21" spans="1:20" ht="45" customHeight="1">
-      <c r="A21" s="106"/>
-      <c r="B21" s="159" t="s">
+      <c r="A21" s="117"/>
+      <c r="B21" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="160"/>
-      <c r="D21" s="164" t="s">
+      <c r="C21" s="123"/>
+      <c r="D21" s="101" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="165"/>
-      <c r="F21" s="166" t="s">
+      <c r="E21" s="102"/>
+      <c r="F21" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="167"/>
-      <c r="H21" s="167"/>
-      <c r="I21" s="168"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="159" t="s">
+      <c r="G21" s="104"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="105"/>
+      <c r="K21" s="117"/>
+      <c r="L21" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="M21" s="160"/>
-      <c r="N21" s="164" t="s">
+      <c r="M21" s="123"/>
+      <c r="N21" s="101" t="s">
         <v>62</v>
       </c>
-      <c r="O21" s="165"/>
-      <c r="P21" s="166" t="s">
+      <c r="O21" s="102"/>
+      <c r="P21" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="Q21" s="167"/>
-      <c r="R21" s="167"/>
-      <c r="S21" s="168"/>
+      <c r="Q21" s="104"/>
+      <c r="R21" s="104"/>
+      <c r="S21" s="105"/>
     </row>
     <row r="22" spans="1:20" ht="63.75" customHeight="1">
-      <c r="A22" s="106"/>
+      <c r="A22" s="117"/>
       <c r="B22" s="73"/>
       <c r="C22" s="60"/>
       <c r="D22" s="74"/>
       <c r="E22" s="60"/>
-      <c r="F22" s="169" t="s">
+      <c r="F22" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="G22" s="170"/>
-      <c r="H22" s="170"/>
-      <c r="I22" s="171"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="115"/>
       <c r="J22" s="86"/>
-      <c r="K22" s="106"/>
+      <c r="K22" s="117"/>
       <c r="L22" s="73"/>
       <c r="M22" s="60"/>
       <c r="N22" s="74"/>
       <c r="O22" s="60"/>
-      <c r="P22" s="169" t="s">
+      <c r="P22" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="Q22" s="170"/>
-      <c r="R22" s="170"/>
-      <c r="S22" s="171"/>
+      <c r="Q22" s="114"/>
+      <c r="R22" s="114"/>
+      <c r="S22" s="115"/>
       <c r="T22" s="85"/>
     </row>
     <row r="23" spans="1:20" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A23" s="107"/>
-      <c r="B23" s="161" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="154"/>
-      <c r="D23" s="153" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" s="154"/>
-      <c r="F23" s="155" t="s">
+      <c r="A23" s="118"/>
+      <c r="B23" s="124" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="125"/>
+      <c r="D23" s="126" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="125"/>
+      <c r="F23" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="G23" s="156"/>
-      <c r="H23" s="153" t="s">
-        <v>77</v>
-      </c>
-      <c r="I23" s="157"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="161" t="s">
-        <v>76</v>
-      </c>
-      <c r="M23" s="154"/>
-      <c r="N23" s="153" t="s">
-        <v>74</v>
-      </c>
-      <c r="O23" s="154"/>
-      <c r="P23" s="155" t="s">
+      <c r="G23" s="128"/>
+      <c r="H23" s="126" t="s">
+        <v>109</v>
+      </c>
+      <c r="I23" s="129"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="124" t="s">
+        <v>108</v>
+      </c>
+      <c r="M23" s="125"/>
+      <c r="N23" s="126" t="s">
+        <v>107</v>
+      </c>
+      <c r="O23" s="125"/>
+      <c r="P23" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" s="156"/>
-      <c r="R23" s="153" t="s">
-        <v>75</v>
-      </c>
-      <c r="S23" s="157"/>
+      <c r="Q23" s="128"/>
+      <c r="R23" s="126" t="s">
+        <v>109</v>
+      </c>
+      <c r="S23" s="129"/>
     </row>
     <row r="24" spans="1:20" ht="31.5" customHeight="1">
       <c r="A24" s="67" t="s">
@@ -6601,7 +6610,7 @@
       <c r="P24" s="72"/>
       <c r="Q24" s="72"/>
       <c r="R24" s="72"/>
-      <c r="S24" s="162" t="s">
+      <c r="S24" s="99" t="s">
         <v>53</v>
       </c>
       <c r="T24" s="84"/>
@@ -6624,11 +6633,66 @@
       <c r="P25" s="70"/>
       <c r="Q25" s="70"/>
       <c r="R25" s="70"/>
-      <c r="S25" s="163"/>
+      <c r="S25" s="100"/>
       <c r="T25" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:D13"/>
+    <mergeCell ref="E11:F13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="M11:N13"/>
+    <mergeCell ref="O11:P13"/>
+    <mergeCell ref="K6:K19"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="M9:P9"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:D16"/>
+    <mergeCell ref="E14:F16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:N16"/>
+    <mergeCell ref="O14:P16"/>
+    <mergeCell ref="R14:R16"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="E17:F19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="L17:L19"/>
+    <mergeCell ref="M17:N19"/>
+    <mergeCell ref="O17:P19"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="L23:M23"/>
     <mergeCell ref="S24:S25"/>
     <mergeCell ref="N21:O21"/>
     <mergeCell ref="P21:S21"/>
@@ -6645,61 +6709,6 @@
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="F21:I21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="L17:L19"/>
-    <mergeCell ref="M17:N19"/>
-    <mergeCell ref="O17:P19"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="E17:F19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:D16"/>
-    <mergeCell ref="E14:F16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:N16"/>
-    <mergeCell ref="O14:P16"/>
-    <mergeCell ref="R14:R16"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:D13"/>
-    <mergeCell ref="E11:F13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="M11:N13"/>
-    <mergeCell ref="O11:P13"/>
-    <mergeCell ref="K6:K19"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="M9:P9"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:S3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -6738,83 +6747,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21.5">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="101"/>
-      <c r="K1" s="99" t="s">
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="173"/>
+      <c r="K1" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="100"/>
-      <c r="S1" s="101"/>
+      <c r="L1" s="172"/>
+      <c r="M1" s="172"/>
+      <c r="N1" s="172"/>
+      <c r="O1" s="172"/>
+      <c r="P1" s="172"/>
+      <c r="Q1" s="172"/>
+      <c r="R1" s="172"/>
+      <c r="S1" s="173"/>
     </row>
     <row r="2" spans="1:19" ht="22" thickBot="1">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="174" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="104"/>
-      <c r="K2" s="102" t="s">
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="176"/>
+      <c r="K2" s="174" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="103"/>
-      <c r="S2" s="104"/>
+      <c r="L2" s="175"/>
+      <c r="M2" s="175"/>
+      <c r="N2" s="175"/>
+      <c r="O2" s="175"/>
+      <c r="P2" s="175"/>
+      <c r="Q2" s="175"/>
+      <c r="R2" s="175"/>
+      <c r="S2" s="176"/>
     </row>
     <row r="3" spans="1:19" ht="25" customHeight="1">
-      <c r="A3" s="105">
+      <c r="A3" s="116">
         <v>1</v>
       </c>
-      <c r="B3" s="108" t="s">
+      <c r="B3" s="177" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="110"/>
-      <c r="K3" s="105">
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="179"/>
+      <c r="K3" s="116">
         <v>1</v>
       </c>
-      <c r="L3" s="108" t="s">
+      <c r="L3" s="177" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="109"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="109"/>
-      <c r="P3" s="109"/>
-      <c r="Q3" s="109"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="110"/>
+      <c r="M3" s="178"/>
+      <c r="N3" s="178"/>
+      <c r="O3" s="178"/>
+      <c r="P3" s="178"/>
+      <c r="Q3" s="178"/>
+      <c r="R3" s="178"/>
+      <c r="S3" s="179"/>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
-      <c r="A4" s="106"/>
+      <c r="A4" s="117"/>
       <c r="B4" s="68" t="s">
         <v>44</v>
       </c>
@@ -6831,7 +6840,7 @@
       <c r="I4" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="106"/>
+      <c r="K4" s="117"/>
       <c r="L4" s="68" t="s">
         <v>44</v>
       </c>
@@ -6852,7 +6861,7 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1" thickBot="1">
-      <c r="A5" s="107"/>
+      <c r="A5" s="118"/>
       <c r="B5" s="70" t="s">
         <v>45</v>
       </c>
@@ -6869,7 +6878,7 @@
       <c r="I5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="107"/>
+      <c r="K5" s="118"/>
       <c r="L5" s="70" t="s">
         <v>45</v>
       </c>
@@ -6890,7 +6899,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
-      <c r="A6" s="141">
+      <c r="A6" s="106">
         <v>2</v>
       </c>
       <c r="B6" s="64" t="s">
@@ -6903,7 +6912,7 @@
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
       <c r="I6" s="65"/>
-      <c r="K6" s="141">
+      <c r="K6" s="106">
         <v>2</v>
       </c>
       <c r="L6" s="64" t="s">
@@ -6918,7 +6927,7 @@
       <c r="S6" s="65"/>
     </row>
     <row r="7" spans="1:19" ht="32.25" customHeight="1">
-      <c r="A7" s="141"/>
+      <c r="A7" s="106"/>
       <c r="B7" s="68" t="s">
         <v>48</v>
       </c>
@@ -6926,16 +6935,16 @@
       <c r="D7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="142" t="s">
+      <c r="E7" s="169" t="s">
         <v>88</v>
       </c>
-      <c r="F7" s="142"/>
-      <c r="G7" s="142"/>
-      <c r="H7" s="142"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
       <c r="I7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="141"/>
+      <c r="K7" s="106"/>
       <c r="L7" s="68" t="s">
         <v>48</v>
       </c>
@@ -6943,19 +6952,19 @@
       <c r="N7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="142" t="str">
+      <c r="O7" s="169" t="str">
         <f>E7</f>
         <v>7月10日至7月14日</v>
       </c>
-      <c r="P7" s="142"/>
-      <c r="Q7" s="142"/>
-      <c r="R7" s="142"/>
+      <c r="P7" s="169"/>
+      <c r="Q7" s="169"/>
+      <c r="R7" s="169"/>
       <c r="S7" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="37.5" customHeight="1">
-      <c r="A8" s="141"/>
+      <c r="A8" s="106"/>
       <c r="B8" s="68" t="s">
         <v>51</v>
       </c>
@@ -6968,7 +6977,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
       <c r="I8" s="5"/>
-      <c r="K8" s="141"/>
+      <c r="K8" s="106"/>
       <c r="L8" s="68" t="s">
         <v>51</v>
       </c>
@@ -6984,44 +6993,44 @@
       <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" ht="25" customHeight="1">
-      <c r="A9" s="141"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="68"/>
-      <c r="C9" s="143" t="s">
+      <c r="C9" s="170" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="114"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
       <c r="G9" s="55"/>
-      <c r="H9" s="144" t="s">
+      <c r="H9" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="145"/>
-      <c r="K9" s="141"/>
+      <c r="I9" s="108"/>
+      <c r="K9" s="106"/>
       <c r="L9" s="68"/>
-      <c r="M9" s="143" t="s">
+      <c r="M9" s="170" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="114"/>
-      <c r="O9" s="114"/>
-      <c r="P9" s="114"/>
+      <c r="N9" s="112"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="112"/>
       <c r="Q9" s="55"/>
-      <c r="R9" s="144" t="s">
+      <c r="R9" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="S9" s="145"/>
+      <c r="S9" s="108"/>
     </row>
     <row r="10" spans="1:19" ht="25" customHeight="1">
-      <c r="A10" s="141"/>
+      <c r="A10" s="106"/>
       <c r="B10" s="56"/>
-      <c r="C10" s="111" t="s">
+      <c r="C10" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113" t="s">
+      <c r="D10" s="110"/>
+      <c r="E10" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="114"/>
+      <c r="F10" s="112"/>
       <c r="G10" s="55"/>
       <c r="H10" s="57" t="s">
         <v>23</v>
@@ -7029,16 +7038,16 @@
       <c r="I10" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="141"/>
+      <c r="K10" s="106"/>
       <c r="L10" s="56"/>
-      <c r="M10" s="111" t="s">
+      <c r="M10" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="112"/>
-      <c r="O10" s="113" t="s">
+      <c r="N10" s="110"/>
+      <c r="O10" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="114"/>
+      <c r="P10" s="112"/>
       <c r="Q10" s="55"/>
       <c r="R10" s="57" t="s">
         <v>23</v>
@@ -7048,47 +7057,47 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="28" customHeight="1">
-      <c r="A11" s="141"/>
-      <c r="B11" s="115">
+      <c r="A11" s="106"/>
+      <c r="B11" s="130">
         <v>1</v>
       </c>
-      <c r="C11" s="118" t="s">
+      <c r="C11" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="119"/>
-      <c r="E11" s="124" t="s">
+      <c r="D11" s="134"/>
+      <c r="E11" s="155" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="125"/>
+      <c r="F11" s="140"/>
       <c r="G11" s="59"/>
-      <c r="H11" s="130" t="s">
+      <c r="H11" s="145" t="s">
         <v>97</v>
       </c>
-      <c r="I11" s="133" t="s">
+      <c r="I11" s="151" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="141"/>
-      <c r="L11" s="115">
+      <c r="K11" s="106"/>
+      <c r="L11" s="130">
         <v>1</v>
       </c>
-      <c r="M11" s="118" t="str">
+      <c r="M11" s="133" t="str">
         <f>C11</f>
         <v xml:space="preserve">2025 年7月 10 日    </v>
       </c>
-      <c r="N11" s="119"/>
-      <c r="O11" s="124" t="str">
+      <c r="N11" s="134"/>
+      <c r="O11" s="155" t="str">
         <f>E11</f>
         <v>09:30-13:30(4H)
 14:30-17:00(2H30M)
 6H30M</v>
       </c>
-      <c r="P11" s="136"/>
+      <c r="P11" s="159"/>
       <c r="Q11" s="59"/>
-      <c r="R11" s="130" t="str">
+      <c r="R11" s="145" t="str">
         <f>H11</f>
         <v xml:space="preserve">     2025 年7月 10 日    </v>
       </c>
-      <c r="S11" s="133" t="str">
+      <c r="S11" s="151" t="str">
         <f>I11</f>
         <v>0950-1330(3H40m)
 1400-1715(3H10m)
@@ -7096,87 +7105,87 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="28" customHeight="1">
-      <c r="A12" s="141"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="120"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="127"/>
+      <c r="A12" s="106"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="141"/>
+      <c r="F12" s="142"/>
       <c r="G12" s="61"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="134"/>
-      <c r="K12" s="141"/>
-      <c r="L12" s="116"/>
-      <c r="M12" s="120"/>
-      <c r="N12" s="121"/>
-      <c r="O12" s="137"/>
-      <c r="P12" s="138"/>
+      <c r="H12" s="146"/>
+      <c r="I12" s="149"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="135"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="160"/>
+      <c r="P12" s="161"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="131"/>
-      <c r="S12" s="146"/>
+      <c r="R12" s="146"/>
+      <c r="S12" s="152"/>
     </row>
     <row r="13" spans="1:19" ht="28" customHeight="1">
-      <c r="A13" s="141"/>
-      <c r="B13" s="117"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="129"/>
+      <c r="A13" s="106"/>
+      <c r="B13" s="154"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="156"/>
+      <c r="F13" s="157"/>
       <c r="G13" s="60"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="135"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="117"/>
-      <c r="M13" s="122"/>
-      <c r="N13" s="123"/>
-      <c r="O13" s="139"/>
-      <c r="P13" s="140"/>
+      <c r="H13" s="147"/>
+      <c r="I13" s="158"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="154"/>
+      <c r="M13" s="137"/>
+      <c r="N13" s="138"/>
+      <c r="O13" s="162"/>
+      <c r="P13" s="163"/>
       <c r="Q13" s="60"/>
-      <c r="R13" s="132"/>
-      <c r="S13" s="147"/>
+      <c r="R13" s="147"/>
+      <c r="S13" s="153"/>
     </row>
     <row r="14" spans="1:19" ht="28" customHeight="1">
-      <c r="A14" s="141"/>
-      <c r="B14" s="115">
+      <c r="A14" s="106"/>
+      <c r="B14" s="130">
         <v>2</v>
       </c>
-      <c r="C14" s="118" t="s">
+      <c r="C14" s="133" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="119"/>
-      <c r="E14" s="124" t="s">
+      <c r="D14" s="134"/>
+      <c r="E14" s="155" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="125"/>
+      <c r="F14" s="140"/>
       <c r="G14" s="59"/>
-      <c r="H14" s="130" t="s">
+      <c r="H14" s="145" t="s">
         <v>94</v>
       </c>
-      <c r="I14" s="133" t="s">
+      <c r="I14" s="151" t="s">
         <v>96</v>
       </c>
-      <c r="K14" s="141"/>
-      <c r="L14" s="115">
+      <c r="K14" s="106"/>
+      <c r="L14" s="130">
         <v>2</v>
       </c>
-      <c r="M14" s="118" t="str">
+      <c r="M14" s="133" t="str">
         <f>C14</f>
         <v xml:space="preserve">2025年 7 月  14 日    </v>
       </c>
-      <c r="N14" s="119"/>
-      <c r="O14" s="124" t="str">
+      <c r="N14" s="134"/>
+      <c r="O14" s="155" t="str">
         <f>E14</f>
         <v>09:30-13:30(4H)
 14:30-18:00(3H30M)
 7H30M</v>
       </c>
-      <c r="P14" s="136"/>
+      <c r="P14" s="159"/>
       <c r="Q14" s="59"/>
-      <c r="R14" s="130" t="str">
+      <c r="R14" s="145" t="str">
         <f>H14</f>
         <v xml:space="preserve">2025年 7 月  14 日        </v>
       </c>
-      <c r="S14" s="133" t="str">
+      <c r="S14" s="151" t="str">
         <f>I14</f>
         <v>0930-1330(4H)
 18:00-21:10(3H10M)
@@ -7184,238 +7193,238 @@
       </c>
     </row>
     <row r="15" spans="1:19" ht="28" customHeight="1">
-      <c r="A15" s="141"/>
-      <c r="B15" s="116"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="127"/>
+      <c r="A15" s="106"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="142"/>
       <c r="G15" s="61"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="134"/>
-      <c r="K15" s="141"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="137"/>
-      <c r="P15" s="138"/>
+      <c r="H15" s="146"/>
+      <c r="I15" s="149"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="131"/>
+      <c r="M15" s="135"/>
+      <c r="N15" s="136"/>
+      <c r="O15" s="160"/>
+      <c r="P15" s="161"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="131"/>
-      <c r="S15" s="146"/>
+      <c r="R15" s="146"/>
+      <c r="S15" s="152"/>
     </row>
     <row r="16" spans="1:19" ht="28" customHeight="1">
-      <c r="A16" s="141"/>
-      <c r="B16" s="117"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="129"/>
+      <c r="A16" s="106"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="156"/>
+      <c r="F16" s="157"/>
       <c r="G16" s="60"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="135"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="122"/>
-      <c r="N16" s="123"/>
-      <c r="O16" s="139"/>
-      <c r="P16" s="140"/>
+      <c r="H16" s="147"/>
+      <c r="I16" s="158"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="154"/>
+      <c r="M16" s="137"/>
+      <c r="N16" s="138"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="163"/>
       <c r="Q16" s="60"/>
-      <c r="R16" s="132"/>
-      <c r="S16" s="147"/>
+      <c r="R16" s="147"/>
+      <c r="S16" s="153"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1">
-      <c r="A17" s="141"/>
-      <c r="B17" s="115">
+      <c r="A17" s="106"/>
+      <c r="B17" s="130">
         <v>3</v>
       </c>
-      <c r="C17" s="118" t="s">
+      <c r="C17" s="133" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="119"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="125"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="140"/>
       <c r="G17" s="59"/>
-      <c r="H17" s="130" t="s">
+      <c r="H17" s="145" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="158"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="115">
+      <c r="I17" s="148"/>
+      <c r="K17" s="106"/>
+      <c r="L17" s="130">
         <v>3</v>
       </c>
-      <c r="M17" s="118" t="s">
+      <c r="M17" s="133" t="s">
         <v>73</v>
       </c>
-      <c r="N17" s="119"/>
-      <c r="O17" s="149"/>
-      <c r="P17" s="125"/>
+      <c r="N17" s="134"/>
+      <c r="O17" s="139"/>
+      <c r="P17" s="140"/>
       <c r="Q17" s="59"/>
-      <c r="R17" s="130" t="s">
+      <c r="R17" s="145" t="s">
         <v>73</v>
       </c>
-      <c r="S17" s="158"/>
+      <c r="S17" s="148"/>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1">
-      <c r="A18" s="141"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="120"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="126"/>
-      <c r="F18" s="127"/>
+      <c r="A18" s="106"/>
+      <c r="B18" s="131"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="136"/>
+      <c r="E18" s="141"/>
+      <c r="F18" s="142"/>
       <c r="G18" s="61"/>
-      <c r="H18" s="131"/>
-      <c r="I18" s="134"/>
-      <c r="K18" s="141"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="126"/>
-      <c r="P18" s="127"/>
+      <c r="H18" s="146"/>
+      <c r="I18" s="149"/>
+      <c r="K18" s="106"/>
+      <c r="L18" s="131"/>
+      <c r="M18" s="135"/>
+      <c r="N18" s="136"/>
+      <c r="O18" s="141"/>
+      <c r="P18" s="142"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="131"/>
-      <c r="S18" s="134"/>
+      <c r="R18" s="146"/>
+      <c r="S18" s="149"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" thickBot="1">
-      <c r="A19" s="141"/>
-      <c r="B19" s="148"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="151"/>
+      <c r="A19" s="106"/>
+      <c r="B19" s="132"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="144"/>
       <c r="G19" s="62"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="152"/>
-      <c r="K19" s="141"/>
-      <c r="L19" s="148"/>
-      <c r="M19" s="122"/>
-      <c r="N19" s="123"/>
-      <c r="O19" s="150"/>
-      <c r="P19" s="151"/>
+      <c r="H19" s="147"/>
+      <c r="I19" s="150"/>
+      <c r="K19" s="106"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="137"/>
+      <c r="N19" s="138"/>
+      <c r="O19" s="143"/>
+      <c r="P19" s="144"/>
       <c r="Q19" s="62"/>
-      <c r="R19" s="132"/>
-      <c r="S19" s="152"/>
+      <c r="R19" s="147"/>
+      <c r="S19" s="150"/>
     </row>
     <row r="20" spans="1:20" ht="20.25" customHeight="1">
-      <c r="A20" s="105">
+      <c r="A20" s="116">
         <v>3</v>
       </c>
-      <c r="B20" s="172" t="s">
+      <c r="B20" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="173"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="173"/>
-      <c r="I20" s="174"/>
-      <c r="K20" s="105">
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="121"/>
+      <c r="K20" s="116">
         <v>3</v>
       </c>
-      <c r="L20" s="172" t="s">
+      <c r="L20" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="M20" s="173"/>
-      <c r="N20" s="173"/>
-      <c r="O20" s="173"/>
-      <c r="P20" s="173"/>
-      <c r="Q20" s="173"/>
-      <c r="R20" s="173"/>
-      <c r="S20" s="174"/>
+      <c r="M20" s="120"/>
+      <c r="N20" s="120"/>
+      <c r="O20" s="120"/>
+      <c r="P20" s="120"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="120"/>
+      <c r="S20" s="121"/>
     </row>
     <row r="21" spans="1:20" ht="45" customHeight="1">
-      <c r="A21" s="106"/>
-      <c r="B21" s="159" t="s">
+      <c r="A21" s="117"/>
+      <c r="B21" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="160"/>
-      <c r="D21" s="164" t="s">
+      <c r="C21" s="123"/>
+      <c r="D21" s="101" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="165"/>
-      <c r="F21" s="166" t="s">
+      <c r="E21" s="102"/>
+      <c r="F21" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="167"/>
-      <c r="H21" s="167"/>
-      <c r="I21" s="168"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="159" t="s">
+      <c r="G21" s="104"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="105"/>
+      <c r="K21" s="117"/>
+      <c r="L21" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="M21" s="160"/>
-      <c r="N21" s="164" t="s">
+      <c r="M21" s="123"/>
+      <c r="N21" s="101" t="s">
         <v>62</v>
       </c>
-      <c r="O21" s="165"/>
-      <c r="P21" s="166" t="s">
+      <c r="O21" s="102"/>
+      <c r="P21" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="Q21" s="167"/>
-      <c r="R21" s="167"/>
-      <c r="S21" s="168"/>
+      <c r="Q21" s="104"/>
+      <c r="R21" s="104"/>
+      <c r="S21" s="105"/>
     </row>
     <row r="22" spans="1:20" ht="63.75" customHeight="1">
-      <c r="A22" s="106"/>
+      <c r="A22" s="117"/>
       <c r="B22" s="73"/>
       <c r="C22" s="60"/>
       <c r="D22" s="74"/>
       <c r="E22" s="60"/>
-      <c r="F22" s="169" t="s">
+      <c r="F22" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="G22" s="170"/>
-      <c r="H22" s="170"/>
-      <c r="I22" s="171"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="115"/>
       <c r="J22" s="86"/>
-      <c r="K22" s="106"/>
+      <c r="K22" s="117"/>
       <c r="L22" s="73"/>
       <c r="M22" s="60"/>
       <c r="N22" s="74"/>
       <c r="O22" s="60"/>
-      <c r="P22" s="169" t="s">
+      <c r="P22" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="Q22" s="170"/>
-      <c r="R22" s="170"/>
-      <c r="S22" s="171"/>
+      <c r="Q22" s="114"/>
+      <c r="R22" s="114"/>
+      <c r="S22" s="115"/>
       <c r="T22" s="85"/>
     </row>
     <row r="23" spans="1:20" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A23" s="107"/>
-      <c r="B23" s="161" t="s">
+      <c r="A23" s="118"/>
+      <c r="B23" s="124" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="154"/>
-      <c r="D23" s="153" t="s">
+      <c r="C23" s="125"/>
+      <c r="D23" s="126" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="154"/>
-      <c r="F23" s="155" t="s">
+      <c r="E23" s="125"/>
+      <c r="F23" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="G23" s="156"/>
-      <c r="H23" s="153" t="s">
+      <c r="G23" s="128"/>
+      <c r="H23" s="126" t="s">
         <v>77</v>
       </c>
-      <c r="I23" s="157"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="161" t="s">
+      <c r="I23" s="129"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="124" t="s">
         <v>76</v>
       </c>
-      <c r="M23" s="154"/>
-      <c r="N23" s="153" t="s">
+      <c r="M23" s="125"/>
+      <c r="N23" s="126" t="s">
         <v>74</v>
       </c>
-      <c r="O23" s="154"/>
-      <c r="P23" s="155" t="s">
+      <c r="O23" s="125"/>
+      <c r="P23" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" s="156"/>
-      <c r="R23" s="153" t="s">
+      <c r="Q23" s="128"/>
+      <c r="R23" s="126" t="s">
         <v>75</v>
       </c>
-      <c r="S23" s="157"/>
+      <c r="S23" s="129"/>
     </row>
     <row r="24" spans="1:20" ht="31.5" customHeight="1">
       <c r="A24" s="67" t="s">
@@ -7444,7 +7453,7 @@
       <c r="P24" s="72"/>
       <c r="Q24" s="72"/>
       <c r="R24" s="72"/>
-      <c r="S24" s="162" t="s">
+      <c r="S24" s="99" t="s">
         <v>53</v>
       </c>
       <c r="T24" s="84"/>
@@ -7467,19 +7476,58 @@
       <c r="P25" s="70"/>
       <c r="Q25" s="70"/>
       <c r="R25" s="70"/>
-      <c r="S25" s="163"/>
+      <c r="S25" s="100"/>
       <c r="T25" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="K20:K23"/>
+    <mergeCell ref="L20:S20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="L17:L19"/>
+    <mergeCell ref="M17:N19"/>
+    <mergeCell ref="O17:P19"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="E17:F19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:D16"/>
+    <mergeCell ref="E14:F16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:N16"/>
+    <mergeCell ref="O14:P16"/>
+    <mergeCell ref="R14:R16"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="M11:N13"/>
+    <mergeCell ref="O11:P13"/>
+    <mergeCell ref="R11:R13"/>
     <mergeCell ref="A6:A19"/>
     <mergeCell ref="K6:K19"/>
     <mergeCell ref="E7:H7"/>
@@ -7496,53 +7544,14 @@
     <mergeCell ref="C11:D13"/>
     <mergeCell ref="E11:F13"/>
     <mergeCell ref="H11:H13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:D16"/>
-    <mergeCell ref="E14:F16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:N16"/>
-    <mergeCell ref="O14:P16"/>
-    <mergeCell ref="R14:R16"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="M11:N13"/>
-    <mergeCell ref="O11:P13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="E17:F19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="L17:L19"/>
-    <mergeCell ref="M17:N19"/>
-    <mergeCell ref="O17:P19"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="K20:K23"/>
-    <mergeCell ref="L20:S20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="S24:S25"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:S3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -7583,83 +7592,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="184.5" customHeight="1">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="230" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="177"/>
-      <c r="K1" s="175" t="s">
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="231"/>
+      <c r="F1" s="231"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="232"/>
+      <c r="K1" s="230" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="176"/>
-      <c r="M1" s="176"/>
-      <c r="N1" s="176"/>
-      <c r="O1" s="176"/>
-      <c r="P1" s="176"/>
-      <c r="Q1" s="176"/>
-      <c r="R1" s="176"/>
-      <c r="S1" s="177"/>
+      <c r="L1" s="231"/>
+      <c r="M1" s="231"/>
+      <c r="N1" s="231"/>
+      <c r="O1" s="231"/>
+      <c r="P1" s="231"/>
+      <c r="Q1" s="231"/>
+      <c r="R1" s="231"/>
+      <c r="S1" s="232"/>
     </row>
     <row r="2" spans="1:19" ht="139.5" customHeight="1" thickBot="1">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="233" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="179"/>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="179"/>
-      <c r="H2" s="179"/>
-      <c r="I2" s="180"/>
-      <c r="K2" s="178" t="s">
+      <c r="B2" s="234"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="234"/>
+      <c r="I2" s="235"/>
+      <c r="K2" s="233" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="179"/>
-      <c r="M2" s="179"/>
-      <c r="N2" s="179"/>
-      <c r="O2" s="179"/>
-      <c r="P2" s="179"/>
-      <c r="Q2" s="179"/>
-      <c r="R2" s="179"/>
-      <c r="S2" s="180"/>
+      <c r="L2" s="234"/>
+      <c r="M2" s="234"/>
+      <c r="N2" s="234"/>
+      <c r="O2" s="234"/>
+      <c r="P2" s="234"/>
+      <c r="Q2" s="234"/>
+      <c r="R2" s="234"/>
+      <c r="S2" s="235"/>
     </row>
     <row r="3" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A3" s="181">
+      <c r="A3" s="180">
         <v>1</v>
       </c>
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="237" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="186"/>
-      <c r="K3" s="181">
+      <c r="C3" s="238"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="238"/>
+      <c r="H3" s="238"/>
+      <c r="I3" s="239"/>
+      <c r="K3" s="180">
         <v>1</v>
       </c>
-      <c r="L3" s="184" t="s">
+      <c r="L3" s="237" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="185"/>
-      <c r="N3" s="185"/>
-      <c r="O3" s="185"/>
-      <c r="P3" s="185"/>
-      <c r="Q3" s="185"/>
-      <c r="R3" s="185"/>
-      <c r="S3" s="186"/>
+      <c r="M3" s="238"/>
+      <c r="N3" s="238"/>
+      <c r="O3" s="238"/>
+      <c r="P3" s="238"/>
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="239"/>
     </row>
     <row r="4" spans="1:19" s="12" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A4" s="182"/>
+      <c r="A4" s="181"/>
       <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
@@ -7676,7 +7685,7 @@
         <v>79</v>
       </c>
       <c r="I4" s="11"/>
-      <c r="K4" s="182"/>
+      <c r="K4" s="181"/>
       <c r="L4" s="8" t="s">
         <v>19</v>
       </c>
@@ -7695,7 +7704,7 @@
       <c r="S4" s="11"/>
     </row>
     <row r="5" spans="1:19" s="12" customFormat="1" ht="222" customHeight="1" thickBot="1">
-      <c r="A5" s="183"/>
+      <c r="A5" s="236"/>
       <c r="B5" s="13" t="s">
         <v>17</v>
       </c>
@@ -7712,7 +7721,7 @@
         <v>80</v>
       </c>
       <c r="I5" s="16"/>
-      <c r="K5" s="183"/>
+      <c r="K5" s="236"/>
       <c r="L5" s="13" t="s">
         <v>17</v>
       </c>
@@ -7731,7 +7740,7 @@
       <c r="S5" s="16"/>
     </row>
     <row r="6" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A6" s="218">
+      <c r="A6" s="204">
         <v>2</v>
       </c>
       <c r="B6" s="17" t="s">
@@ -7744,7 +7753,7 @@
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
       <c r="I6" s="19"/>
-      <c r="K6" s="218">
+      <c r="K6" s="204">
         <v>2</v>
       </c>
       <c r="L6" s="17" t="s">
@@ -7759,36 +7768,36 @@
       <c r="S6" s="19"/>
     </row>
     <row r="7" spans="1:19" s="12" customFormat="1" ht="207" customHeight="1">
-      <c r="A7" s="219"/>
-      <c r="B7" s="222" t="s">
+      <c r="A7" s="205"/>
+      <c r="B7" s="214" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="223"/>
-      <c r="D7" s="223"/>
-      <c r="E7" s="223"/>
+      <c r="C7" s="215"/>
+      <c r="D7" s="215"/>
+      <c r="E7" s="215"/>
       <c r="F7" s="90"/>
-      <c r="G7" s="235" t="s">
+      <c r="G7" s="240" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="235"/>
-      <c r="I7" s="236"/>
-      <c r="K7" s="219"/>
-      <c r="L7" s="222" t="s">
+      <c r="H7" s="240"/>
+      <c r="I7" s="241"/>
+      <c r="K7" s="205"/>
+      <c r="L7" s="214" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="223"/>
-      <c r="N7" s="223"/>
-      <c r="O7" s="223"/>
+      <c r="M7" s="215"/>
+      <c r="N7" s="215"/>
+      <c r="O7" s="215"/>
       <c r="P7" s="90"/>
-      <c r="Q7" s="235" t="str">
+      <c r="Q7" s="240" t="str">
         <f>G7</f>
         <v>7月22日  至 to  8月25日 (包括當天 )</v>
       </c>
-      <c r="R7" s="235"/>
-      <c r="S7" s="236"/>
+      <c r="R7" s="240"/>
+      <c r="S7" s="241"/>
     </row>
     <row r="8" spans="1:19" s="12" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A8" s="219"/>
+      <c r="A8" s="205"/>
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
@@ -7805,7 +7814,7 @@
         <v>36</v>
       </c>
       <c r="I8" s="11"/>
-      <c r="K8" s="219"/>
+      <c r="K8" s="205"/>
       <c r="L8" s="8" t="s">
         <v>13</v>
       </c>
@@ -7826,7 +7835,7 @@
       <c r="S8" s="11"/>
     </row>
     <row r="9" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A9" s="219"/>
+      <c r="A9" s="205"/>
       <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
@@ -7843,7 +7852,7 @@
       <c r="I9" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="219"/>
+      <c r="K9" s="205"/>
       <c r="L9" s="8" t="s">
         <v>12</v>
       </c>
@@ -7862,7 +7871,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A10" s="219"/>
+      <c r="A10" s="205"/>
       <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
@@ -7881,7 +7890,7 @@
       <c r="I10" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="K10" s="219"/>
+      <c r="K10" s="205"/>
       <c r="L10" s="28" t="s">
         <v>8</v>
       </c>
@@ -7905,8 +7914,8 @@
       </c>
     </row>
     <row r="11" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A11" s="219"/>
-      <c r="B11" s="212" t="s">
+      <c r="A11" s="205"/>
+      <c r="B11" s="198" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="34" t="s">
@@ -7924,8 +7933,8 @@
       <c r="I11" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="K11" s="219"/>
-      <c r="L11" s="212" t="s">
+      <c r="K11" s="205"/>
+      <c r="L11" s="198" t="s">
         <v>7</v>
       </c>
       <c r="M11" s="34" t="s">
@@ -7948,8 +7957,8 @@
       </c>
     </row>
     <row r="12" spans="1:19" s="27" customFormat="1" ht="147" customHeight="1">
-      <c r="A12" s="219"/>
-      <c r="B12" s="213"/>
+      <c r="A12" s="205"/>
+      <c r="B12" s="199"/>
       <c r="C12" s="34" t="s">
         <v>30</v>
       </c>
@@ -7959,8 +7968,8 @@
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
       <c r="I12" s="33"/>
-      <c r="K12" s="219"/>
-      <c r="L12" s="213"/>
+      <c r="K12" s="205"/>
+      <c r="L12" s="199"/>
       <c r="M12" s="34" t="s">
         <v>30</v>
       </c>
@@ -7972,60 +7981,60 @@
       <c r="S12" s="33"/>
     </row>
     <row r="13" spans="1:19" s="27" customFormat="1" ht="154.5" customHeight="1">
-      <c r="A13" s="219"/>
-      <c r="B13" s="214"/>
-      <c r="C13" s="215" t="s">
+      <c r="A13" s="205"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="201" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="216"/>
-      <c r="E13" s="216"/>
-      <c r="F13" s="217"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="202"/>
+      <c r="F13" s="203"/>
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
       <c r="I13" s="33"/>
-      <c r="K13" s="219"/>
-      <c r="L13" s="214"/>
-      <c r="M13" s="215" t="s">
+      <c r="K13" s="205"/>
+      <c r="L13" s="200"/>
+      <c r="M13" s="201" t="s">
         <v>6</v>
       </c>
-      <c r="N13" s="216"/>
-      <c r="O13" s="216"/>
-      <c r="P13" s="217"/>
+      <c r="N13" s="202"/>
+      <c r="O13" s="202"/>
+      <c r="P13" s="203"/>
       <c r="Q13" s="32"/>
       <c r="R13" s="32"/>
       <c r="S13" s="33"/>
     </row>
     <row r="14" spans="1:19" s="27" customFormat="1" ht="219.75" customHeight="1">
-      <c r="A14" s="219"/>
-      <c r="B14" s="212" t="s">
+      <c r="A14" s="205"/>
+      <c r="B14" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="197" t="s">
+      <c r="C14" s="211" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="198"/>
-      <c r="E14" s="198"/>
-      <c r="F14" s="199"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
+      <c r="F14" s="213"/>
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
       <c r="I14" s="33"/>
-      <c r="K14" s="219"/>
-      <c r="L14" s="212" t="s">
+      <c r="K14" s="205"/>
+      <c r="L14" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="197" t="s">
+      <c r="M14" s="211" t="s">
         <v>68</v>
       </c>
-      <c r="N14" s="198"/>
-      <c r="O14" s="198"/>
-      <c r="P14" s="199"/>
+      <c r="N14" s="212"/>
+      <c r="O14" s="212"/>
+      <c r="P14" s="213"/>
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="33"/>
     </row>
     <row r="15" spans="1:19" s="27" customFormat="1" ht="157.5" customHeight="1">
-      <c r="A15" s="219"/>
-      <c r="B15" s="213"/>
+      <c r="A15" s="205"/>
+      <c r="B15" s="199"/>
       <c r="C15" s="34" t="s">
         <v>31</v>
       </c>
@@ -8035,8 +8044,8 @@
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
-      <c r="K15" s="219"/>
-      <c r="L15" s="213"/>
+      <c r="K15" s="205"/>
+      <c r="L15" s="199"/>
       <c r="M15" s="34" t="s">
         <v>31</v>
       </c>
@@ -8048,8 +8057,8 @@
       <c r="S15" s="33"/>
     </row>
     <row r="16" spans="1:19" s="27" customFormat="1" ht="120" customHeight="1">
-      <c r="A16" s="219"/>
-      <c r="B16" s="213"/>
+      <c r="A16" s="205"/>
+      <c r="B16" s="199"/>
       <c r="C16" s="34" t="s">
         <v>32</v>
       </c>
@@ -8059,8 +8068,8 @@
       <c r="G16" s="38"/>
       <c r="H16" s="77"/>
       <c r="I16" s="78"/>
-      <c r="K16" s="219"/>
-      <c r="L16" s="213"/>
+      <c r="K16" s="205"/>
+      <c r="L16" s="199"/>
       <c r="M16" s="34" t="s">
         <v>32</v>
       </c>
@@ -8072,8 +8081,8 @@
       <c r="S16" s="78"/>
     </row>
     <row r="17" spans="1:19" s="27" customFormat="1" ht="112.5" customHeight="1">
-      <c r="A17" s="219"/>
-      <c r="B17" s="213"/>
+      <c r="A17" s="205"/>
+      <c r="B17" s="199"/>
       <c r="C17" s="34" t="s">
         <v>37</v>
       </c>
@@ -8083,8 +8092,8 @@
       <c r="G17" s="38"/>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="K17" s="219"/>
-      <c r="L17" s="213"/>
+      <c r="K17" s="205"/>
+      <c r="L17" s="199"/>
       <c r="M17" s="34" t="s">
         <v>37</v>
       </c>
@@ -8096,32 +8105,32 @@
       <c r="S17" s="40"/>
     </row>
     <row r="18" spans="1:19" s="27" customFormat="1" ht="165" customHeight="1">
-      <c r="A18" s="219"/>
-      <c r="B18" s="213"/>
-      <c r="C18" s="194" t="s">
+      <c r="A18" s="205"/>
+      <c r="B18" s="199"/>
+      <c r="C18" s="208" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="195"/>
-      <c r="E18" s="195"/>
-      <c r="F18" s="196"/>
+      <c r="D18" s="209"/>
+      <c r="E18" s="209"/>
+      <c r="F18" s="210"/>
       <c r="G18" s="41"/>
       <c r="H18" s="41"/>
       <c r="I18" s="42"/>
-      <c r="K18" s="219"/>
-      <c r="L18" s="213"/>
-      <c r="M18" s="194" t="s">
+      <c r="K18" s="205"/>
+      <c r="L18" s="199"/>
+      <c r="M18" s="208" t="s">
         <v>38</v>
       </c>
-      <c r="N18" s="195"/>
-      <c r="O18" s="195"/>
-      <c r="P18" s="196"/>
+      <c r="N18" s="209"/>
+      <c r="O18" s="209"/>
+      <c r="P18" s="210"/>
       <c r="Q18" s="41"/>
       <c r="R18" s="41"/>
       <c r="S18" s="42"/>
     </row>
     <row r="19" spans="1:19" s="27" customFormat="1" ht="157.5" customHeight="1">
-      <c r="A19" s="219"/>
-      <c r="B19" s="213"/>
+      <c r="A19" s="205"/>
+      <c r="B19" s="199"/>
       <c r="C19" s="43" t="s">
         <v>4</v>
       </c>
@@ -8131,8 +8140,8 @@
       <c r="G19" s="44"/>
       <c r="H19" s="44"/>
       <c r="I19" s="40"/>
-      <c r="K19" s="219"/>
-      <c r="L19" s="213"/>
+      <c r="K19" s="205"/>
+      <c r="L19" s="199"/>
       <c r="M19" s="43" t="s">
         <v>4</v>
       </c>
@@ -8144,8 +8153,8 @@
       <c r="S19" s="40"/>
     </row>
     <row r="20" spans="1:19" s="27" customFormat="1" ht="150" customHeight="1">
-      <c r="A20" s="219"/>
-      <c r="B20" s="213"/>
+      <c r="A20" s="205"/>
+      <c r="B20" s="199"/>
       <c r="C20" s="34" t="s">
         <v>33</v>
       </c>
@@ -8155,8 +8164,8 @@
       <c r="G20" s="45"/>
       <c r="H20" s="45"/>
       <c r="I20" s="46"/>
-      <c r="K20" s="219"/>
-      <c r="L20" s="213"/>
+      <c r="K20" s="205"/>
+      <c r="L20" s="199"/>
       <c r="M20" s="34" t="s">
         <v>33</v>
       </c>
@@ -8168,8 +8177,8 @@
       <c r="S20" s="46"/>
     </row>
     <row r="21" spans="1:19" s="27" customFormat="1" ht="127.5" customHeight="1" thickBot="1">
-      <c r="A21" s="220"/>
-      <c r="B21" s="221"/>
+      <c r="A21" s="206"/>
+      <c r="B21" s="207"/>
       <c r="C21" s="34" t="s">
         <v>34</v>
       </c>
@@ -8179,8 +8188,8 @@
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
       <c r="I21" s="47"/>
-      <c r="K21" s="220"/>
-      <c r="L21" s="221"/>
+      <c r="K21" s="206"/>
+      <c r="L21" s="207"/>
       <c r="M21" s="34" t="s">
         <v>34</v>
       </c>
@@ -8192,85 +8201,85 @@
       <c r="S21" s="47"/>
     </row>
     <row r="22" spans="1:19" s="7" customFormat="1" ht="132" customHeight="1">
-      <c r="A22" s="181">
+      <c r="A22" s="180">
         <v>3</v>
       </c>
-      <c r="B22" s="224" t="s">
+      <c r="B22" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="225"/>
-      <c r="D22" s="225"/>
-      <c r="E22" s="225"/>
-      <c r="F22" s="225"/>
-      <c r="G22" s="225"/>
-      <c r="H22" s="225"/>
-      <c r="I22" s="226"/>
-      <c r="K22" s="181">
+      <c r="C22" s="183"/>
+      <c r="D22" s="183"/>
+      <c r="E22" s="183"/>
+      <c r="F22" s="183"/>
+      <c r="G22" s="183"/>
+      <c r="H22" s="183"/>
+      <c r="I22" s="184"/>
+      <c r="K22" s="180">
         <v>3</v>
       </c>
-      <c r="L22" s="224" t="s">
+      <c r="L22" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="225"/>
-      <c r="N22" s="225"/>
-      <c r="O22" s="225"/>
-      <c r="P22" s="225"/>
-      <c r="Q22" s="225"/>
-      <c r="R22" s="225"/>
-      <c r="S22" s="226"/>
+      <c r="M22" s="183"/>
+      <c r="N22" s="183"/>
+      <c r="O22" s="183"/>
+      <c r="P22" s="183"/>
+      <c r="Q22" s="183"/>
+      <c r="R22" s="183"/>
+      <c r="S22" s="184"/>
     </row>
     <row r="23" spans="1:19" s="27" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A23" s="182"/>
-      <c r="B23" s="227" t="s">
+      <c r="A23" s="181"/>
+      <c r="B23" s="185" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="228"/>
-      <c r="D23" s="206" t="s">
+      <c r="C23" s="186"/>
+      <c r="D23" s="187" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="229"/>
-      <c r="F23" s="228"/>
-      <c r="G23" s="206" t="s">
+      <c r="E23" s="188"/>
+      <c r="F23" s="186"/>
+      <c r="G23" s="187" t="s">
         <v>55</v>
       </c>
-      <c r="H23" s="207"/>
+      <c r="H23" s="189"/>
       <c r="I23" s="48"/>
-      <c r="K23" s="182"/>
-      <c r="L23" s="227" t="s">
+      <c r="K23" s="181"/>
+      <c r="L23" s="185" t="s">
         <v>58</v>
       </c>
-      <c r="M23" s="228"/>
-      <c r="N23" s="206" t="s">
+      <c r="M23" s="186"/>
+      <c r="N23" s="187" t="s">
         <v>63</v>
       </c>
-      <c r="O23" s="229"/>
-      <c r="P23" s="228"/>
-      <c r="Q23" s="206" t="s">
+      <c r="O23" s="188"/>
+      <c r="P23" s="186"/>
+      <c r="Q23" s="187" t="s">
         <v>55</v>
       </c>
-      <c r="R23" s="207"/>
+      <c r="R23" s="189"/>
       <c r="S23" s="48"/>
     </row>
     <row r="24" spans="1:19" s="27" customFormat="1" ht="199.5" customHeight="1">
-      <c r="A24" s="182"/>
+      <c r="A24" s="181"/>
       <c r="B24" s="89"/>
       <c r="C24" s="88"/>
-      <c r="D24" s="232" t="s">
+      <c r="D24" s="195" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="233"/>
-      <c r="F24" s="234"/>
+      <c r="E24" s="196"/>
+      <c r="F24" s="197"/>
       <c r="G24" s="87"/>
       <c r="H24" s="49" t="s">
         <v>39</v>
       </c>
       <c r="I24" s="48"/>
-      <c r="K24" s="182"/>
+      <c r="K24" s="181"/>
       <c r="L24" s="89"/>
       <c r="M24" s="79"/>
-      <c r="N24" s="232"/>
-      <c r="O24" s="233"/>
-      <c r="P24" s="234"/>
+      <c r="N24" s="195"/>
+      <c r="O24" s="196"/>
+      <c r="P24" s="197"/>
       <c r="Q24" s="87"/>
       <c r="R24" s="49" t="s">
         <v>39</v>
@@ -8278,65 +8287,65 @@
       <c r="S24" s="48"/>
     </row>
     <row r="25" spans="1:19" s="27" customFormat="1" ht="124.5" customHeight="1">
-      <c r="A25" s="182"/>
+      <c r="A25" s="181"/>
       <c r="B25" s="80"/>
       <c r="C25" s="81"/>
       <c r="D25" s="82"/>
       <c r="E25" s="83"/>
       <c r="F25" s="81"/>
       <c r="G25" s="96"/>
-      <c r="H25" s="189" t="s">
+      <c r="H25" s="224" t="s">
         <v>67</v>
       </c>
-      <c r="I25" s="190"/>
-      <c r="K25" s="182"/>
+      <c r="I25" s="225"/>
+      <c r="K25" s="181"/>
       <c r="L25" s="51"/>
       <c r="M25" s="91"/>
       <c r="N25" s="82"/>
       <c r="O25" s="83"/>
       <c r="P25" s="81"/>
       <c r="Q25" s="96"/>
-      <c r="R25" s="189" t="s">
+      <c r="R25" s="224" t="s">
         <v>2</v>
       </c>
-      <c r="S25" s="190"/>
+      <c r="S25" s="225"/>
     </row>
     <row r="26" spans="1:19" s="27" customFormat="1" ht="274.5" customHeight="1" thickBot="1">
-      <c r="A26" s="182"/>
-      <c r="B26" s="230" t="s">
+      <c r="A26" s="181"/>
+      <c r="B26" s="193" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="231"/>
-      <c r="D26" s="191" t="s">
+      <c r="C26" s="194"/>
+      <c r="D26" s="190" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="192"/>
-      <c r="F26" s="193"/>
+      <c r="E26" s="191"/>
+      <c r="F26" s="192"/>
       <c r="G26" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="208" t="s">
+      <c r="H26" s="226" t="s">
         <v>71</v>
       </c>
-      <c r="I26" s="209"/>
+      <c r="I26" s="227"/>
       <c r="J26" s="93"/>
-      <c r="K26" s="182"/>
-      <c r="L26" s="230" t="s">
+      <c r="K26" s="181"/>
+      <c r="L26" s="193" t="s">
         <v>69</v>
       </c>
-      <c r="M26" s="231"/>
-      <c r="N26" s="191" t="s">
+      <c r="M26" s="194"/>
+      <c r="N26" s="190" t="s">
         <v>70</v>
       </c>
-      <c r="O26" s="192"/>
-      <c r="P26" s="193"/>
+      <c r="O26" s="191"/>
+      <c r="P26" s="192"/>
       <c r="Q26" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="R26" s="210" t="s">
+      <c r="R26" s="228" t="s">
         <v>71</v>
       </c>
-      <c r="S26" s="211"/>
+      <c r="S26" s="229"/>
     </row>
     <row r="27" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
       <c r="A27" s="50" t="s">
@@ -8360,10 +8369,10 @@
       <c r="O27" s="92"/>
       <c r="P27" s="92"/>
       <c r="Q27" s="92"/>
-      <c r="R27" s="200" t="s">
+      <c r="R27" s="218" t="s">
         <v>40</v>
       </c>
-      <c r="S27" s="201"/>
+      <c r="S27" s="219"/>
     </row>
     <row r="28" spans="1:19" s="27" customFormat="1" ht="106.5" customHeight="1">
       <c r="A28" s="51"/>
@@ -8375,8 +8384,8 @@
       <c r="M28" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="R28" s="202"/>
-      <c r="S28" s="203"/>
+      <c r="R28" s="220"/>
+      <c r="S28" s="221"/>
     </row>
     <row r="29" spans="1:19" ht="79.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A29" s="52"/>
@@ -8396,8 +8405,8 @@
       <c r="O29" s="53"/>
       <c r="P29" s="53"/>
       <c r="Q29" s="53"/>
-      <c r="R29" s="204"/>
-      <c r="S29" s="205"/>
+      <c r="R29" s="222"/>
+      <c r="S29" s="223"/>
     </row>
     <row r="50" spans="13:13">
       <c r="M50" s="94"/>
@@ -8407,14 +8416,29 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="R27:S29"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="K22:K26"/>
+    <mergeCell ref="L22:S22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
     <mergeCell ref="A6:A21"/>
     <mergeCell ref="K6:K21"/>
     <mergeCell ref="B7:E7"/>
@@ -8429,29 +8453,14 @@
     <mergeCell ref="M14:P14"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="M18:P18"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="K22:K26"/>
-    <mergeCell ref="L22:S22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R27:S29"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:S3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/M15_Template.xlsx
+++ b/public/M15_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kyler\OneDrive\桌面\mss_ai_department\mss_ai_department\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0046EC81-9D47-4C8F-9FA5-131FBCD3627E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712BCED1-685D-47E9-9725-3D1CF7BC6287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="599" activeTab="1" xr2:uid="{99967081-488D-44D6-94DC-7450F6337A9B}"/>
   </bookViews>
@@ -2033,7 +2033,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2331,6 +2331,210 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2352,27 +2556,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2382,15 +2565,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2400,185 +2574,152 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2595,24 +2736,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2628,136 +2754,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5035,83 +5041,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="200.15" customHeight="1">
-      <c r="A1" s="230" t="s">
+      <c r="A1" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="231"/>
-      <c r="C1" s="231"/>
-      <c r="D1" s="231"/>
-      <c r="E1" s="231"/>
-      <c r="F1" s="231"/>
-      <c r="G1" s="231"/>
-      <c r="H1" s="231"/>
-      <c r="I1" s="232"/>
-      <c r="K1" s="230" t="s">
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="182"/>
+      <c r="K1" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="231"/>
-      <c r="M1" s="231"/>
-      <c r="N1" s="231"/>
-      <c r="O1" s="231"/>
-      <c r="P1" s="231"/>
-      <c r="Q1" s="231"/>
-      <c r="R1" s="231"/>
-      <c r="S1" s="232"/>
+      <c r="L1" s="181"/>
+      <c r="M1" s="181"/>
+      <c r="N1" s="181"/>
+      <c r="O1" s="181"/>
+      <c r="P1" s="181"/>
+      <c r="Q1" s="181"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="182"/>
     </row>
     <row r="2" spans="1:19" ht="200.15" customHeight="1" thickBot="1">
-      <c r="A2" s="233" t="s">
+      <c r="A2" s="183" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="234"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="234"/>
-      <c r="H2" s="234"/>
-      <c r="I2" s="235"/>
-      <c r="K2" s="233" t="s">
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="185"/>
+      <c r="K2" s="183" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="234"/>
-      <c r="M2" s="234"/>
-      <c r="N2" s="234"/>
-      <c r="O2" s="234"/>
-      <c r="P2" s="234"/>
-      <c r="Q2" s="234"/>
-      <c r="R2" s="234"/>
-      <c r="S2" s="235"/>
+      <c r="L2" s="184"/>
+      <c r="M2" s="184"/>
+      <c r="N2" s="184"/>
+      <c r="O2" s="184"/>
+      <c r="P2" s="184"/>
+      <c r="Q2" s="184"/>
+      <c r="R2" s="184"/>
+      <c r="S2" s="185"/>
     </row>
     <row r="3" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A3" s="180">
+      <c r="A3" s="186">
         <v>1</v>
       </c>
-      <c r="B3" s="237" t="s">
+      <c r="B3" s="189" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="238"/>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="238"/>
-      <c r="I3" s="239"/>
-      <c r="K3" s="180">
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+      <c r="I3" s="191"/>
+      <c r="K3" s="186">
         <v>1</v>
       </c>
-      <c r="L3" s="237" t="s">
+      <c r="L3" s="189" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="238"/>
-      <c r="N3" s="238"/>
-      <c r="O3" s="238"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="239"/>
+      <c r="M3" s="190"/>
+      <c r="N3" s="190"/>
+      <c r="O3" s="190"/>
+      <c r="P3" s="190"/>
+      <c r="Q3" s="190"/>
+      <c r="R3" s="190"/>
+      <c r="S3" s="191"/>
     </row>
     <row r="4" spans="1:19" s="12" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A4" s="181"/>
+      <c r="A4" s="187"/>
       <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
@@ -5128,7 +5134,7 @@
         <v>79</v>
       </c>
       <c r="I4" s="11"/>
-      <c r="K4" s="181"/>
+      <c r="K4" s="187"/>
       <c r="L4" s="8" t="s">
         <v>19</v>
       </c>
@@ -5147,7 +5153,7 @@
       <c r="S4" s="11"/>
     </row>
     <row r="5" spans="1:19" s="12" customFormat="1" ht="222" customHeight="1" thickBot="1">
-      <c r="A5" s="236"/>
+      <c r="A5" s="188"/>
       <c r="B5" s="13" t="s">
         <v>17</v>
       </c>
@@ -5164,7 +5170,7 @@
         <v>80</v>
       </c>
       <c r="I5" s="16"/>
-      <c r="K5" s="236"/>
+      <c r="K5" s="188"/>
       <c r="L5" s="13" t="s">
         <v>17</v>
       </c>
@@ -5183,7 +5189,7 @@
       <c r="S5" s="16"/>
     </row>
     <row r="6" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A6" s="204">
+      <c r="A6" s="223">
         <v>2</v>
       </c>
       <c r="B6" s="17" t="s">
@@ -5196,7 +5202,7 @@
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
       <c r="I6" s="19"/>
-      <c r="K6" s="204">
+      <c r="K6" s="223">
         <v>2</v>
       </c>
       <c r="L6" s="17" t="s">
@@ -5211,43 +5217,43 @@
       <c r="S6" s="19"/>
     </row>
     <row r="7" spans="1:19" s="12" customFormat="1" ht="289.5" customHeight="1">
-      <c r="A7" s="205"/>
-      <c r="B7" s="214" t="s">
+      <c r="A7" s="224"/>
+      <c r="B7" s="227" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="215"/>
-      <c r="D7" s="215"/>
-      <c r="E7" s="215"/>
+      <c r="C7" s="228"/>
+      <c r="D7" s="228"/>
+      <c r="E7" s="228"/>
       <c r="F7" s="90" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="H7" s="216" t="s">
+      <c r="H7" s="192" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="217"/>
-      <c r="K7" s="205"/>
-      <c r="L7" s="214" t="s">
+      <c r="I7" s="193"/>
+      <c r="K7" s="224"/>
+      <c r="L7" s="227" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="215"/>
-      <c r="N7" s="215"/>
-      <c r="O7" s="215"/>
+      <c r="M7" s="228"/>
+      <c r="N7" s="228"/>
+      <c r="O7" s="228"/>
       <c r="P7" s="90" t="s">
         <v>82</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="R7" s="216" t="s">
+      <c r="R7" s="192" t="s">
         <v>85</v>
       </c>
-      <c r="S7" s="217"/>
+      <c r="S7" s="193"/>
     </row>
     <row r="8" spans="1:19" s="12" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A8" s="205"/>
+      <c r="A8" s="224"/>
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
@@ -5264,7 +5270,7 @@
         <v>36</v>
       </c>
       <c r="I8" s="11"/>
-      <c r="K8" s="205"/>
+      <c r="K8" s="224"/>
       <c r="L8" s="8" t="s">
         <v>13</v>
       </c>
@@ -5283,7 +5289,7 @@
       <c r="S8" s="11"/>
     </row>
     <row r="9" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A9" s="205"/>
+      <c r="A9" s="224"/>
       <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
@@ -5300,7 +5306,7 @@
       <c r="I9" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="205"/>
+      <c r="K9" s="224"/>
       <c r="L9" s="8" t="s">
         <v>12</v>
       </c>
@@ -5319,7 +5325,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A10" s="205"/>
+      <c r="A10" s="224"/>
       <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
@@ -5336,7 +5342,7 @@
         <v>1800</v>
       </c>
       <c r="I10" s="33"/>
-      <c r="K10" s="205"/>
+      <c r="K10" s="224"/>
       <c r="L10" s="28" t="s">
         <v>8</v>
       </c>
@@ -5355,8 +5361,8 @@
       <c r="S10" s="33"/>
     </row>
     <row r="11" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A11" s="205"/>
-      <c r="B11" s="198" t="s">
+      <c r="A11" s="224"/>
+      <c r="B11" s="217" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="34" t="s">
@@ -5368,8 +5374,8 @@
       <c r="G11" s="36"/>
       <c r="H11" s="36"/>
       <c r="I11" s="37"/>
-      <c r="K11" s="205"/>
-      <c r="L11" s="198" t="s">
+      <c r="K11" s="224"/>
+      <c r="L11" s="217" t="s">
         <v>7</v>
       </c>
       <c r="M11" s="34" t="s">
@@ -5383,8 +5389,8 @@
       <c r="S11" s="37"/>
     </row>
     <row r="12" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A12" s="205"/>
-      <c r="B12" s="199"/>
+      <c r="A12" s="224"/>
+      <c r="B12" s="218"/>
       <c r="C12" s="34" t="s">
         <v>30</v>
       </c>
@@ -5394,8 +5400,8 @@
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
       <c r="I12" s="33"/>
-      <c r="K12" s="205"/>
-      <c r="L12" s="199"/>
+      <c r="K12" s="224"/>
+      <c r="L12" s="218"/>
       <c r="M12" s="34" t="s">
         <v>30</v>
       </c>
@@ -5407,60 +5413,60 @@
       <c r="S12" s="33"/>
     </row>
     <row r="13" spans="1:19" s="27" customFormat="1" ht="199.5" customHeight="1">
-      <c r="A13" s="205"/>
-      <c r="B13" s="200"/>
-      <c r="C13" s="201" t="s">
+      <c r="A13" s="224"/>
+      <c r="B13" s="219"/>
+      <c r="C13" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="202"/>
-      <c r="E13" s="202"/>
-      <c r="F13" s="203"/>
+      <c r="D13" s="221"/>
+      <c r="E13" s="221"/>
+      <c r="F13" s="222"/>
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
       <c r="I13" s="33"/>
-      <c r="K13" s="205"/>
-      <c r="L13" s="200"/>
-      <c r="M13" s="201" t="s">
+      <c r="K13" s="224"/>
+      <c r="L13" s="219"/>
+      <c r="M13" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="N13" s="202"/>
-      <c r="O13" s="202"/>
-      <c r="P13" s="203"/>
+      <c r="N13" s="221"/>
+      <c r="O13" s="221"/>
+      <c r="P13" s="222"/>
       <c r="Q13" s="32"/>
       <c r="R13" s="32"/>
       <c r="S13" s="33"/>
     </row>
     <row r="14" spans="1:19" s="27" customFormat="1" ht="250" customHeight="1">
-      <c r="A14" s="205"/>
-      <c r="B14" s="198" t="s">
+      <c r="A14" s="224"/>
+      <c r="B14" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="211" t="s">
+      <c r="C14" s="202" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-      <c r="F14" s="213"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="204"/>
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
       <c r="I14" s="33"/>
-      <c r="K14" s="205"/>
-      <c r="L14" s="198" t="s">
+      <c r="K14" s="224"/>
+      <c r="L14" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="211" t="s">
+      <c r="M14" s="202" t="s">
         <v>68</v>
       </c>
-      <c r="N14" s="212"/>
-      <c r="O14" s="212"/>
-      <c r="P14" s="213"/>
+      <c r="N14" s="203"/>
+      <c r="O14" s="203"/>
+      <c r="P14" s="204"/>
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="33"/>
     </row>
     <row r="15" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A15" s="205"/>
-      <c r="B15" s="199"/>
+      <c r="A15" s="224"/>
+      <c r="B15" s="218"/>
       <c r="C15" s="34" t="s">
         <v>31</v>
       </c>
@@ -5470,8 +5476,8 @@
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
-      <c r="K15" s="205"/>
-      <c r="L15" s="199"/>
+      <c r="K15" s="224"/>
+      <c r="L15" s="218"/>
       <c r="M15" s="34" t="s">
         <v>31</v>
       </c>
@@ -5483,8 +5489,8 @@
       <c r="S15" s="33"/>
     </row>
     <row r="16" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A16" s="205"/>
-      <c r="B16" s="199"/>
+      <c r="A16" s="224"/>
+      <c r="B16" s="218"/>
       <c r="C16" s="34" t="s">
         <v>32</v>
       </c>
@@ -5494,8 +5500,8 @@
       <c r="G16" s="38"/>
       <c r="H16" s="77"/>
       <c r="I16" s="78"/>
-      <c r="K16" s="205"/>
-      <c r="L16" s="199"/>
+      <c r="K16" s="224"/>
+      <c r="L16" s="218"/>
       <c r="M16" s="34" t="s">
         <v>32</v>
       </c>
@@ -5507,8 +5513,8 @@
       <c r="S16" s="78"/>
     </row>
     <row r="17" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A17" s="205"/>
-      <c r="B17" s="199"/>
+      <c r="A17" s="224"/>
+      <c r="B17" s="218"/>
       <c r="C17" s="34" t="s">
         <v>37</v>
       </c>
@@ -5518,8 +5524,8 @@
       <c r="G17" s="38"/>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="K17" s="205"/>
-      <c r="L17" s="199"/>
+      <c r="K17" s="224"/>
+      <c r="L17" s="218"/>
       <c r="M17" s="34" t="s">
         <v>37</v>
       </c>
@@ -5531,32 +5537,32 @@
       <c r="S17" s="40"/>
     </row>
     <row r="18" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A18" s="205"/>
-      <c r="B18" s="199"/>
-      <c r="C18" s="208" t="s">
+      <c r="A18" s="224"/>
+      <c r="B18" s="218"/>
+      <c r="C18" s="199" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="209"/>
-      <c r="E18" s="209"/>
-      <c r="F18" s="210"/>
+      <c r="D18" s="200"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="201"/>
       <c r="G18" s="41"/>
       <c r="H18" s="41"/>
       <c r="I18" s="42"/>
-      <c r="K18" s="205"/>
-      <c r="L18" s="199"/>
-      <c r="M18" s="208" t="s">
+      <c r="K18" s="224"/>
+      <c r="L18" s="218"/>
+      <c r="M18" s="199" t="s">
         <v>38</v>
       </c>
-      <c r="N18" s="209"/>
-      <c r="O18" s="209"/>
-      <c r="P18" s="210"/>
+      <c r="N18" s="200"/>
+      <c r="O18" s="200"/>
+      <c r="P18" s="201"/>
       <c r="Q18" s="41"/>
       <c r="R18" s="41"/>
       <c r="S18" s="42"/>
     </row>
     <row r="19" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A19" s="205"/>
-      <c r="B19" s="199"/>
+      <c r="A19" s="224"/>
+      <c r="B19" s="218"/>
       <c r="C19" s="43" t="s">
         <v>4</v>
       </c>
@@ -5566,8 +5572,8 @@
       <c r="G19" s="44"/>
       <c r="H19" s="44"/>
       <c r="I19" s="40"/>
-      <c r="K19" s="205"/>
-      <c r="L19" s="199"/>
+      <c r="K19" s="224"/>
+      <c r="L19" s="218"/>
       <c r="M19" s="43" t="s">
         <v>4</v>
       </c>
@@ -5579,8 +5585,8 @@
       <c r="S19" s="40"/>
     </row>
     <row r="20" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A20" s="205"/>
-      <c r="B20" s="199"/>
+      <c r="A20" s="224"/>
+      <c r="B20" s="218"/>
       <c r="C20" s="34" t="s">
         <v>33</v>
       </c>
@@ -5590,8 +5596,8 @@
       <c r="G20" s="45"/>
       <c r="H20" s="45"/>
       <c r="I20" s="46"/>
-      <c r="K20" s="205"/>
-      <c r="L20" s="199"/>
+      <c r="K20" s="224"/>
+      <c r="L20" s="218"/>
       <c r="M20" s="34" t="s">
         <v>33</v>
       </c>
@@ -5603,8 +5609,8 @@
       <c r="S20" s="46"/>
     </row>
     <row r="21" spans="1:19" s="27" customFormat="1" ht="188.15" customHeight="1" thickBot="1">
-      <c r="A21" s="206"/>
-      <c r="B21" s="207"/>
+      <c r="A21" s="225"/>
+      <c r="B21" s="226"/>
       <c r="C21" s="34" t="s">
         <v>34</v>
       </c>
@@ -5614,8 +5620,8 @@
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
       <c r="I21" s="47"/>
-      <c r="K21" s="206"/>
-      <c r="L21" s="207"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="226"/>
       <c r="M21" s="34" t="s">
         <v>34</v>
       </c>
@@ -5627,85 +5633,85 @@
       <c r="S21" s="47"/>
     </row>
     <row r="22" spans="1:19" s="7" customFormat="1" ht="132" customHeight="1">
-      <c r="A22" s="180">
+      <c r="A22" s="186">
         <v>3</v>
       </c>
-      <c r="B22" s="182" t="s">
+      <c r="B22" s="229" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="183"/>
-      <c r="D22" s="183"/>
-      <c r="E22" s="183"/>
-      <c r="F22" s="183"/>
-      <c r="G22" s="183"/>
-      <c r="H22" s="183"/>
-      <c r="I22" s="184"/>
-      <c r="K22" s="180">
+      <c r="C22" s="230"/>
+      <c r="D22" s="230"/>
+      <c r="E22" s="230"/>
+      <c r="F22" s="230"/>
+      <c r="G22" s="230"/>
+      <c r="H22" s="230"/>
+      <c r="I22" s="231"/>
+      <c r="K22" s="186">
         <v>3</v>
       </c>
-      <c r="L22" s="182" t="s">
+      <c r="L22" s="229" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="183"/>
-      <c r="N22" s="183"/>
-      <c r="O22" s="183"/>
-      <c r="P22" s="183"/>
-      <c r="Q22" s="183"/>
-      <c r="R22" s="183"/>
-      <c r="S22" s="184"/>
+      <c r="M22" s="230"/>
+      <c r="N22" s="230"/>
+      <c r="O22" s="230"/>
+      <c r="P22" s="230"/>
+      <c r="Q22" s="230"/>
+      <c r="R22" s="230"/>
+      <c r="S22" s="231"/>
     </row>
     <row r="23" spans="1:19" s="27" customFormat="1" ht="274.5" customHeight="1">
-      <c r="A23" s="181"/>
-      <c r="B23" s="185" t="s">
+      <c r="A23" s="187"/>
+      <c r="B23" s="232" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="186"/>
-      <c r="D23" s="187" t="s">
+      <c r="C23" s="233"/>
+      <c r="D23" s="211" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="188"/>
-      <c r="F23" s="186"/>
-      <c r="G23" s="187" t="s">
+      <c r="E23" s="234"/>
+      <c r="F23" s="233"/>
+      <c r="G23" s="211" t="s">
         <v>55</v>
       </c>
-      <c r="H23" s="189"/>
+      <c r="H23" s="212"/>
       <c r="I23" s="48"/>
-      <c r="K23" s="181"/>
-      <c r="L23" s="185" t="s">
+      <c r="K23" s="187"/>
+      <c r="L23" s="232" t="s">
         <v>58</v>
       </c>
-      <c r="M23" s="186"/>
-      <c r="N23" s="187" t="s">
+      <c r="M23" s="233"/>
+      <c r="N23" s="211" t="s">
         <v>63</v>
       </c>
-      <c r="O23" s="188"/>
-      <c r="P23" s="186"/>
-      <c r="Q23" s="187" t="s">
+      <c r="O23" s="234"/>
+      <c r="P23" s="233"/>
+      <c r="Q23" s="211" t="s">
         <v>56</v>
       </c>
-      <c r="R23" s="189"/>
+      <c r="R23" s="212"/>
       <c r="S23" s="48"/>
     </row>
     <row r="24" spans="1:19" s="27" customFormat="1" ht="267" customHeight="1">
-      <c r="A24" s="181"/>
+      <c r="A24" s="187"/>
       <c r="B24" s="89"/>
       <c r="C24" s="88"/>
-      <c r="D24" s="195" t="s">
+      <c r="D24" s="237" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="196"/>
-      <c r="F24" s="197"/>
+      <c r="E24" s="238"/>
+      <c r="F24" s="239"/>
       <c r="G24" s="87"/>
       <c r="H24" s="49" t="s">
         <v>39</v>
       </c>
       <c r="I24" s="48"/>
-      <c r="K24" s="181"/>
+      <c r="K24" s="187"/>
       <c r="L24" s="89"/>
       <c r="M24" s="79"/>
-      <c r="N24" s="195"/>
-      <c r="O24" s="196"/>
-      <c r="P24" s="197"/>
+      <c r="N24" s="237"/>
+      <c r="O24" s="238"/>
+      <c r="P24" s="239"/>
       <c r="Q24" s="87"/>
       <c r="R24" s="49" t="s">
         <v>39</v>
@@ -5713,65 +5719,65 @@
       <c r="S24" s="48"/>
     </row>
     <row r="25" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A25" s="181"/>
+      <c r="A25" s="187"/>
       <c r="B25" s="80"/>
       <c r="C25" s="81"/>
       <c r="D25" s="82"/>
       <c r="E25" s="83"/>
       <c r="F25" s="81"/>
       <c r="G25" s="96"/>
-      <c r="H25" s="224" t="s">
+      <c r="H25" s="194" t="s">
         <v>67</v>
       </c>
-      <c r="I25" s="225"/>
-      <c r="K25" s="181"/>
+      <c r="I25" s="195"/>
+      <c r="K25" s="187"/>
       <c r="L25" s="51"/>
       <c r="M25" s="91"/>
       <c r="N25" s="82"/>
       <c r="O25" s="83"/>
       <c r="P25" s="81"/>
       <c r="Q25" s="96"/>
-      <c r="R25" s="224" t="s">
+      <c r="R25" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="S25" s="225"/>
+      <c r="S25" s="195"/>
     </row>
     <row r="26" spans="1:19" s="27" customFormat="1" ht="237" customHeight="1" thickBot="1">
-      <c r="A26" s="181"/>
-      <c r="B26" s="193" t="s">
+      <c r="A26" s="187"/>
+      <c r="B26" s="235" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="194"/>
-      <c r="D26" s="190" t="s">
+      <c r="C26" s="236"/>
+      <c r="D26" s="196" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="191"/>
-      <c r="F26" s="192"/>
+      <c r="E26" s="197"/>
+      <c r="F26" s="198"/>
       <c r="G26" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="226" t="s">
+      <c r="H26" s="213" t="s">
         <v>71</v>
       </c>
-      <c r="I26" s="227"/>
+      <c r="I26" s="214"/>
       <c r="J26" s="93"/>
-      <c r="K26" s="181"/>
-      <c r="L26" s="193" t="s">
+      <c r="K26" s="187"/>
+      <c r="L26" s="235" t="s">
         <v>69</v>
       </c>
-      <c r="M26" s="194"/>
-      <c r="N26" s="190" t="s">
+      <c r="M26" s="236"/>
+      <c r="N26" s="196" t="s">
         <v>70</v>
       </c>
-      <c r="O26" s="191"/>
-      <c r="P26" s="192"/>
+      <c r="O26" s="197"/>
+      <c r="P26" s="198"/>
       <c r="Q26" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="R26" s="228" t="s">
+      <c r="R26" s="215" t="s">
         <v>71</v>
       </c>
-      <c r="S26" s="229"/>
+      <c r="S26" s="216"/>
     </row>
     <row r="27" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
       <c r="A27" s="50" t="s">
@@ -5795,10 +5801,10 @@
       <c r="O27" s="92"/>
       <c r="P27" s="92"/>
       <c r="Q27" s="92"/>
-      <c r="R27" s="218" t="s">
+      <c r="R27" s="205" t="s">
         <v>40</v>
       </c>
-      <c r="S27" s="219"/>
+      <c r="S27" s="206"/>
     </row>
     <row r="28" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
       <c r="A28" s="51"/>
@@ -5810,8 +5816,8 @@
       <c r="M28" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="R28" s="220"/>
-      <c r="S28" s="221"/>
+      <c r="R28" s="207"/>
+      <c r="S28" s="208"/>
     </row>
     <row r="29" spans="1:19" ht="79.5" customHeight="1" thickBot="1">
       <c r="A29" s="52"/>
@@ -5831,8 +5837,8 @@
       <c r="O29" s="53"/>
       <c r="P29" s="53"/>
       <c r="Q29" s="53"/>
-      <c r="R29" s="222"/>
-      <c r="S29" s="223"/>
+      <c r="R29" s="209"/>
+      <c r="S29" s="210"/>
     </row>
     <row r="50" spans="13:13">
       <c r="M50" s="94"/>
@@ -5842,37 +5848,6 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:S3"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="M18:P18"/>
-    <mergeCell ref="M14:P14"/>
-    <mergeCell ref="R27:S29"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="A6:A21"/>
-    <mergeCell ref="K6:K21"/>
-    <mergeCell ref="B14:B21"/>
-    <mergeCell ref="L14:L21"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="L7:O7"/>
     <mergeCell ref="A22:A26"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="K22:K26"/>
@@ -5887,6 +5862,37 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="N23:P23"/>
     <mergeCell ref="N24:P24"/>
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="A6:A21"/>
+    <mergeCell ref="K6:K21"/>
+    <mergeCell ref="B14:B21"/>
+    <mergeCell ref="L14:L21"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="R27:S29"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="M14:P14"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="B3:I3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5924,83 +5930,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21.5">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="173"/>
-      <c r="K1" s="171" t="s">
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="101"/>
+      <c r="K1" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="172"/>
-      <c r="R1" s="172"/>
-      <c r="S1" s="173"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="100"/>
+      <c r="S1" s="101"/>
     </row>
     <row r="2" spans="1:19" ht="22" thickBot="1">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="102" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="175"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="176"/>
-      <c r="K2" s="174" t="s">
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="104"/>
+      <c r="K2" s="102" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="175"/>
-      <c r="M2" s="175"/>
-      <c r="N2" s="175"/>
-      <c r="O2" s="175"/>
-      <c r="P2" s="175"/>
-      <c r="Q2" s="175"/>
-      <c r="R2" s="175"/>
-      <c r="S2" s="176"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="104"/>
     </row>
     <row r="3" spans="1:19" ht="25" customHeight="1">
-      <c r="A3" s="116">
+      <c r="A3" s="105">
         <v>1</v>
       </c>
-      <c r="B3" s="177" t="s">
+      <c r="B3" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="179"/>
-      <c r="K3" s="116">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="110"/>
+      <c r="K3" s="105">
         <v>1</v>
       </c>
-      <c r="L3" s="177" t="s">
+      <c r="L3" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="178"/>
-      <c r="N3" s="178"/>
-      <c r="O3" s="178"/>
-      <c r="P3" s="178"/>
-      <c r="Q3" s="178"/>
-      <c r="R3" s="178"/>
-      <c r="S3" s="179"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="109"/>
+      <c r="P3" s="109"/>
+      <c r="Q3" s="109"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="110"/>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
-      <c r="A4" s="117"/>
+      <c r="A4" s="106"/>
       <c r="B4" s="68" t="s">
         <v>44</v>
       </c>
@@ -6013,7 +6019,7 @@
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="5"/>
-      <c r="K4" s="117"/>
+      <c r="K4" s="106"/>
       <c r="L4" s="68" t="s">
         <v>44</v>
       </c>
@@ -6034,7 +6040,7 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1" thickBot="1">
-      <c r="A5" s="118"/>
+      <c r="A5" s="107"/>
       <c r="B5" s="70" t="s">
         <v>45</v>
       </c>
@@ -6047,7 +6053,7 @@
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="3"/>
-      <c r="K5" s="118"/>
+      <c r="K5" s="107"/>
       <c r="L5" s="70" t="s">
         <v>45</v>
       </c>
@@ -6068,7 +6074,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
-      <c r="A6" s="106">
+      <c r="A6" s="146">
         <v>2</v>
       </c>
       <c r="B6" s="64" t="s">
@@ -6081,7 +6087,7 @@
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
       <c r="I6" s="65"/>
-      <c r="K6" s="106">
+      <c r="K6" s="146">
         <v>2</v>
       </c>
       <c r="L6" s="64" t="s">
@@ -6096,7 +6102,7 @@
       <c r="S6" s="65"/>
     </row>
     <row r="7" spans="1:19" ht="32.25" customHeight="1">
-      <c r="A7" s="106"/>
+      <c r="A7" s="146"/>
       <c r="B7" s="68" t="s">
         <v>48</v>
       </c>
@@ -6104,14 +6110,14 @@
       <c r="D7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="169"/>
-      <c r="F7" s="169"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="169"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
       <c r="I7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="106"/>
+      <c r="K7" s="146"/>
       <c r="L7" s="68" t="s">
         <v>48</v>
       </c>
@@ -6119,19 +6125,19 @@
       <c r="N7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="169" t="str">
+      <c r="O7" s="147" t="str">
         <f>IF(E7="","",E7)</f>
         <v/>
       </c>
-      <c r="P7" s="169"/>
-      <c r="Q7" s="169"/>
-      <c r="R7" s="169"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
+      <c r="R7" s="147"/>
       <c r="S7" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="37.5" customHeight="1">
-      <c r="A8" s="106"/>
+      <c r="A8" s="146"/>
       <c r="B8" s="68" t="s">
         <v>51</v>
       </c>
@@ -6142,7 +6148,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
       <c r="I8" s="5"/>
-      <c r="K8" s="106"/>
+      <c r="K8" s="146"/>
       <c r="L8" s="68" t="s">
         <v>51</v>
       </c>
@@ -6158,44 +6164,44 @@
       <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" ht="25" customHeight="1">
-      <c r="A9" s="106"/>
+      <c r="A9" s="146"/>
       <c r="B9" s="68"/>
-      <c r="C9" s="170" t="s">
+      <c r="C9" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
+      <c r="D9" s="114"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="114"/>
       <c r="G9" s="55"/>
-      <c r="H9" s="107" t="s">
+      <c r="H9" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="108"/>
-      <c r="K9" s="106"/>
+      <c r="I9" s="150"/>
+      <c r="K9" s="146"/>
       <c r="L9" s="68"/>
-      <c r="M9" s="170" t="s">
+      <c r="M9" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="112"/>
-      <c r="O9" s="112"/>
-      <c r="P9" s="112"/>
+      <c r="N9" s="114"/>
+      <c r="O9" s="114"/>
+      <c r="P9" s="114"/>
       <c r="Q9" s="55"/>
-      <c r="R9" s="107" t="s">
+      <c r="R9" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="S9" s="108"/>
+      <c r="S9" s="150"/>
     </row>
     <row r="10" spans="1:19" ht="25" customHeight="1">
-      <c r="A10" s="106"/>
+      <c r="A10" s="146"/>
       <c r="B10" s="56"/>
-      <c r="C10" s="109" t="s">
+      <c r="C10" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111" t="s">
+      <c r="D10" s="112"/>
+      <c r="E10" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="112"/>
+      <c r="F10" s="114"/>
       <c r="G10" s="55"/>
       <c r="H10" s="57" t="s">
         <v>23</v>
@@ -6203,16 +6209,16 @@
       <c r="I10" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="106"/>
+      <c r="K10" s="146"/>
       <c r="L10" s="56"/>
-      <c r="M10" s="109" t="s">
+      <c r="M10" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="110"/>
-      <c r="O10" s="111" t="s">
+      <c r="N10" s="112"/>
+      <c r="O10" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="112"/>
+      <c r="P10" s="114"/>
       <c r="Q10" s="55"/>
       <c r="R10" s="57" t="s">
         <v>23</v>
@@ -6222,366 +6228,366 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="28" customHeight="1">
-      <c r="A11" s="106"/>
-      <c r="B11" s="130">
+      <c r="A11" s="146"/>
+      <c r="B11" s="115">
         <v>1</v>
       </c>
-      <c r="C11" s="133" t="s">
+      <c r="C11" s="118" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="164"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="140"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="125"/>
       <c r="G11" s="59"/>
-      <c r="H11" s="145" t="s">
+      <c r="H11" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="I11" s="151"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="130">
+      <c r="I11" s="133"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="115">
         <v>1</v>
       </c>
-      <c r="M11" s="133" t="str">
+      <c r="M11" s="118" t="str">
         <f>C11</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="N11" s="134"/>
-      <c r="O11" s="155" t="str">
+      <c r="N11" s="136"/>
+      <c r="O11" s="124" t="str">
         <f>IF(E11="","",E11)</f>
         <v/>
       </c>
-      <c r="P11" s="159"/>
+      <c r="P11" s="141"/>
       <c r="Q11" s="59"/>
-      <c r="R11" s="145" t="str">
+      <c r="R11" s="130" t="str">
         <f>H11</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="S11" s="151" t="str">
+      <c r="S11" s="133" t="str">
         <f>IF(I11="","",I11)</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:19" ht="28" customHeight="1">
-      <c r="A12" s="106"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="165"/>
-      <c r="D12" s="166"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="142"/>
+      <c r="A12" s="146"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="127"/>
       <c r="G12" s="61"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="149"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="131"/>
-      <c r="M12" s="135"/>
-      <c r="N12" s="136"/>
-      <c r="O12" s="160"/>
-      <c r="P12" s="161"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="134"/>
+      <c r="K12" s="146"/>
+      <c r="L12" s="116"/>
+      <c r="M12" s="137"/>
+      <c r="N12" s="138"/>
+      <c r="O12" s="142"/>
+      <c r="P12" s="143"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="146"/>
-      <c r="S12" s="152"/>
+      <c r="R12" s="131"/>
+      <c r="S12" s="151"/>
     </row>
     <row r="13" spans="1:19" ht="28" customHeight="1">
-      <c r="A13" s="106"/>
-      <c r="B13" s="154"/>
-      <c r="C13" s="167"/>
-      <c r="D13" s="168"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="157"/>
+      <c r="A13" s="146"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="128"/>
+      <c r="F13" s="129"/>
       <c r="G13" s="60"/>
-      <c r="H13" s="147"/>
-      <c r="I13" s="158"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="154"/>
-      <c r="M13" s="137"/>
-      <c r="N13" s="138"/>
-      <c r="O13" s="162"/>
-      <c r="P13" s="163"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="135"/>
+      <c r="K13" s="146"/>
+      <c r="L13" s="117"/>
+      <c r="M13" s="139"/>
+      <c r="N13" s="140"/>
+      <c r="O13" s="144"/>
+      <c r="P13" s="145"/>
       <c r="Q13" s="60"/>
-      <c r="R13" s="147"/>
-      <c r="S13" s="153"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="152"/>
     </row>
     <row r="14" spans="1:19" ht="28" customHeight="1">
-      <c r="A14" s="106"/>
-      <c r="B14" s="130">
+      <c r="A14" s="146"/>
+      <c r="B14" s="115">
         <v>2</v>
       </c>
-      <c r="C14" s="133" t="s">
+      <c r="C14" s="118" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="134"/>
-      <c r="E14" s="155"/>
-      <c r="F14" s="140"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="125"/>
       <c r="G14" s="59"/>
-      <c r="H14" s="145" t="s">
+      <c r="H14" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="I14" s="151"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="130">
+      <c r="I14" s="133"/>
+      <c r="K14" s="146"/>
+      <c r="L14" s="115">
         <v>2</v>
       </c>
-      <c r="M14" s="133" t="str">
+      <c r="M14" s="118" t="str">
         <f>C14</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="N14" s="134"/>
-      <c r="O14" s="155" t="str">
+      <c r="N14" s="136"/>
+      <c r="O14" s="124" t="str">
         <f>IF(E14="","",E14)</f>
         <v/>
       </c>
-      <c r="P14" s="159"/>
+      <c r="P14" s="141"/>
       <c r="Q14" s="59"/>
-      <c r="R14" s="145" t="str">
+      <c r="R14" s="130" t="str">
         <f>H14</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="S14" s="151" t="str">
+      <c r="S14" s="133" t="str">
         <f>IF(I14="","",I14)</f>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:19" ht="28" customHeight="1">
-      <c r="A15" s="106"/>
-      <c r="B15" s="131"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="142"/>
+      <c r="A15" s="146"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="127"/>
       <c r="G15" s="61"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="149"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="131"/>
-      <c r="M15" s="135"/>
-      <c r="N15" s="136"/>
-      <c r="O15" s="160"/>
-      <c r="P15" s="161"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="134"/>
+      <c r="K15" s="146"/>
+      <c r="L15" s="116"/>
+      <c r="M15" s="137"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="142"/>
+      <c r="P15" s="143"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="146"/>
-      <c r="S15" s="152"/>
+      <c r="R15" s="131"/>
+      <c r="S15" s="151"/>
     </row>
     <row r="16" spans="1:19" ht="28" customHeight="1">
-      <c r="A16" s="106"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="137"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="156"/>
-      <c r="F16" s="157"/>
+      <c r="A16" s="146"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="139"/>
+      <c r="D16" s="140"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="129"/>
       <c r="G16" s="60"/>
-      <c r="H16" s="147"/>
-      <c r="I16" s="158"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="154"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="138"/>
-      <c r="O16" s="162"/>
-      <c r="P16" s="163"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="135"/>
+      <c r="K16" s="146"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="139"/>
+      <c r="N16" s="140"/>
+      <c r="O16" s="144"/>
+      <c r="P16" s="145"/>
       <c r="Q16" s="60"/>
-      <c r="R16" s="147"/>
-      <c r="S16" s="153"/>
+      <c r="R16" s="132"/>
+      <c r="S16" s="152"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1">
-      <c r="A17" s="106"/>
-      <c r="B17" s="130">
+      <c r="A17" s="146"/>
+      <c r="B17" s="115">
         <v>3</v>
       </c>
-      <c r="C17" s="133" t="s">
+      <c r="C17" s="118" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="134"/>
-      <c r="E17" s="139"/>
-      <c r="F17" s="140"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="154"/>
+      <c r="F17" s="125"/>
       <c r="G17" s="59"/>
-      <c r="H17" s="145" t="s">
+      <c r="H17" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="I17" s="151"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="130">
+      <c r="I17" s="133"/>
+      <c r="K17" s="146"/>
+      <c r="L17" s="115">
         <v>3</v>
       </c>
-      <c r="M17" s="133" t="str">
+      <c r="M17" s="118" t="str">
         <f>C17</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="N17" s="134"/>
-      <c r="O17" s="139" t="str">
+      <c r="N17" s="136"/>
+      <c r="O17" s="154" t="str">
         <f>IF(E17="","",E17)</f>
         <v/>
       </c>
-      <c r="P17" s="140"/>
+      <c r="P17" s="125"/>
       <c r="Q17" s="59"/>
-      <c r="R17" s="145" t="str">
+      <c r="R17" s="130" t="str">
         <f>H17</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="S17" s="148" t="str">
+      <c r="S17" s="163" t="str">
         <f>IF(I17="","",I17)</f>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1">
-      <c r="A18" s="106"/>
-      <c r="B18" s="131"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="136"/>
-      <c r="E18" s="141"/>
-      <c r="F18" s="142"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="138"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="127"/>
       <c r="G18" s="61"/>
-      <c r="H18" s="146"/>
-      <c r="I18" s="149"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="131"/>
-      <c r="M18" s="135"/>
-      <c r="N18" s="136"/>
-      <c r="O18" s="141"/>
-      <c r="P18" s="142"/>
+      <c r="H18" s="131"/>
+      <c r="I18" s="134"/>
+      <c r="K18" s="146"/>
+      <c r="L18" s="116"/>
+      <c r="M18" s="137"/>
+      <c r="N18" s="138"/>
+      <c r="O18" s="126"/>
+      <c r="P18" s="127"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="146"/>
-      <c r="S18" s="149"/>
+      <c r="R18" s="131"/>
+      <c r="S18" s="134"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" thickBot="1">
-      <c r="A19" s="106"/>
-      <c r="B19" s="132"/>
-      <c r="C19" s="137"/>
-      <c r="D19" s="138"/>
-      <c r="E19" s="143"/>
-      <c r="F19" s="144"/>
+      <c r="A19" s="146"/>
+      <c r="B19" s="153"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="156"/>
       <c r="G19" s="62"/>
-      <c r="H19" s="147"/>
-      <c r="I19" s="150"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="132"/>
-      <c r="M19" s="137"/>
-      <c r="N19" s="138"/>
-      <c r="O19" s="143"/>
-      <c r="P19" s="144"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="157"/>
+      <c r="K19" s="146"/>
+      <c r="L19" s="153"/>
+      <c r="M19" s="139"/>
+      <c r="N19" s="140"/>
+      <c r="O19" s="155"/>
+      <c r="P19" s="156"/>
       <c r="Q19" s="62"/>
-      <c r="R19" s="147"/>
-      <c r="S19" s="150"/>
+      <c r="R19" s="132"/>
+      <c r="S19" s="157"/>
     </row>
     <row r="20" spans="1:20" ht="20.25" customHeight="1">
-      <c r="A20" s="116">
+      <c r="A20" s="105">
         <v>3</v>
       </c>
-      <c r="B20" s="119" t="s">
+      <c r="B20" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="121"/>
-      <c r="K20" s="116">
+      <c r="C20" s="178"/>
+      <c r="D20" s="178"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="178"/>
+      <c r="G20" s="178"/>
+      <c r="H20" s="178"/>
+      <c r="I20" s="179"/>
+      <c r="K20" s="105">
         <v>3</v>
       </c>
-      <c r="L20" s="119" t="s">
+      <c r="L20" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="M20" s="120"/>
-      <c r="N20" s="120"/>
-      <c r="O20" s="120"/>
-      <c r="P20" s="120"/>
-      <c r="Q20" s="120"/>
-      <c r="R20" s="120"/>
-      <c r="S20" s="121"/>
+      <c r="M20" s="178"/>
+      <c r="N20" s="178"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="178"/>
+      <c r="Q20" s="178"/>
+      <c r="R20" s="178"/>
+      <c r="S20" s="179"/>
     </row>
     <row r="21" spans="1:20" ht="45" customHeight="1">
-      <c r="A21" s="117"/>
-      <c r="B21" s="122" t="s">
+      <c r="A21" s="106"/>
+      <c r="B21" s="164" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="123"/>
-      <c r="D21" s="101" t="s">
+      <c r="C21" s="165"/>
+      <c r="D21" s="169" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="102"/>
-      <c r="F21" s="103" t="s">
+      <c r="E21" s="170"/>
+      <c r="F21" s="171" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="104"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="105"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="122" t="s">
+      <c r="G21" s="172"/>
+      <c r="H21" s="172"/>
+      <c r="I21" s="173"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="164" t="s">
         <v>61</v>
       </c>
-      <c r="M21" s="123"/>
-      <c r="N21" s="101" t="s">
+      <c r="M21" s="165"/>
+      <c r="N21" s="169" t="s">
         <v>62</v>
       </c>
-      <c r="O21" s="102"/>
-      <c r="P21" s="103" t="s">
+      <c r="O21" s="170"/>
+      <c r="P21" s="171" t="s">
         <v>57</v>
       </c>
-      <c r="Q21" s="104"/>
-      <c r="R21" s="104"/>
-      <c r="S21" s="105"/>
+      <c r="Q21" s="172"/>
+      <c r="R21" s="172"/>
+      <c r="S21" s="173"/>
     </row>
     <row r="22" spans="1:20" ht="63.75" customHeight="1">
-      <c r="A22" s="117"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="60"/>
+      <c r="A22" s="106"/>
+      <c r="B22" s="242"/>
+      <c r="C22" s="243"/>
       <c r="D22" s="74"/>
       <c r="E22" s="60"/>
-      <c r="F22" s="113" t="s">
+      <c r="F22" s="174" t="s">
         <v>66</v>
       </c>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="115"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="175"/>
+      <c r="I22" s="176"/>
       <c r="J22" s="86"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="73"/>
-      <c r="M22" s="60"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="242"/>
+      <c r="M22" s="243"/>
       <c r="N22" s="74"/>
       <c r="O22" s="60"/>
-      <c r="P22" s="113" t="s">
+      <c r="P22" s="174" t="s">
         <v>65</v>
       </c>
-      <c r="Q22" s="114"/>
-      <c r="R22" s="114"/>
-      <c r="S22" s="115"/>
+      <c r="Q22" s="175"/>
+      <c r="R22" s="175"/>
+      <c r="S22" s="176"/>
       <c r="T22" s="85"/>
     </row>
     <row r="23" spans="1:20" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A23" s="118"/>
-      <c r="B23" s="124" t="s">
+      <c r="A23" s="107"/>
+      <c r="B23" s="166" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="125"/>
-      <c r="D23" s="126" t="s">
+      <c r="C23" s="159"/>
+      <c r="D23" s="158" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="125"/>
-      <c r="F23" s="127" t="s">
+      <c r="E23" s="159"/>
+      <c r="F23" s="160" t="s">
         <v>54</v>
       </c>
-      <c r="G23" s="128"/>
-      <c r="H23" s="126" t="s">
+      <c r="G23" s="161"/>
+      <c r="H23" s="158" t="s">
         <v>109</v>
       </c>
-      <c r="I23" s="129"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="124" t="s">
+      <c r="I23" s="162"/>
+      <c r="K23" s="107"/>
+      <c r="L23" s="166" t="s">
         <v>108</v>
       </c>
-      <c r="M23" s="125"/>
-      <c r="N23" s="126" t="s">
+      <c r="M23" s="159"/>
+      <c r="N23" s="158" t="s">
         <v>107</v>
       </c>
-      <c r="O23" s="125"/>
-      <c r="P23" s="127" t="s">
+      <c r="O23" s="159"/>
+      <c r="P23" s="160" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" s="128"/>
-      <c r="R23" s="126" t="s">
+      <c r="Q23" s="161"/>
+      <c r="R23" s="158" t="s">
         <v>109</v>
       </c>
-      <c r="S23" s="129"/>
+      <c r="S23" s="162"/>
     </row>
     <row r="24" spans="1:20" ht="31.5" customHeight="1">
       <c r="A24" s="67" t="s">
@@ -6610,7 +6616,7 @@
       <c r="P24" s="72"/>
       <c r="Q24" s="72"/>
       <c r="R24" s="72"/>
-      <c r="S24" s="99" t="s">
+      <c r="S24" s="167" t="s">
         <v>53</v>
       </c>
       <c r="T24" s="84"/>
@@ -6633,19 +6639,60 @@
       <c r="P25" s="70"/>
       <c r="Q25" s="70"/>
       <c r="R25" s="70"/>
-      <c r="S25" s="100"/>
+      <c r="S25" s="168"/>
       <c r="T25" s="84"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:S3"/>
+  <mergeCells count="73">
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="A6:A19"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="K20:K23"/>
+    <mergeCell ref="L20:S20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="L17:L19"/>
+    <mergeCell ref="M17:N19"/>
+    <mergeCell ref="O17:P19"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="E17:F19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:D16"/>
+    <mergeCell ref="E14:F16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:N16"/>
+    <mergeCell ref="O14:P16"/>
+    <mergeCell ref="R14:R16"/>
+    <mergeCell ref="S14:S16"/>
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="O10:P10"/>
     <mergeCell ref="B11:B13"/>
@@ -6662,53 +6709,14 @@
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="M9:P9"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:D16"/>
-    <mergeCell ref="E14:F16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:N16"/>
-    <mergeCell ref="O14:P16"/>
-    <mergeCell ref="R14:R16"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="E17:F19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="L17:L19"/>
-    <mergeCell ref="M17:N19"/>
-    <mergeCell ref="O17:P19"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="S24:S25"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="A6:A19"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="P22:S22"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="K20:K23"/>
-    <mergeCell ref="L20:S20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:S3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -6747,83 +6755,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21.5">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="173"/>
-      <c r="K1" s="171" t="s">
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="101"/>
+      <c r="K1" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="172"/>
-      <c r="R1" s="172"/>
-      <c r="S1" s="173"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="100"/>
+      <c r="S1" s="101"/>
     </row>
     <row r="2" spans="1:19" ht="22" thickBot="1">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="102" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="175"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="176"/>
-      <c r="K2" s="174" t="s">
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="104"/>
+      <c r="K2" s="102" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="175"/>
-      <c r="M2" s="175"/>
-      <c r="N2" s="175"/>
-      <c r="O2" s="175"/>
-      <c r="P2" s="175"/>
-      <c r="Q2" s="175"/>
-      <c r="R2" s="175"/>
-      <c r="S2" s="176"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="104"/>
     </row>
     <row r="3" spans="1:19" ht="25" customHeight="1">
-      <c r="A3" s="116">
+      <c r="A3" s="105">
         <v>1</v>
       </c>
-      <c r="B3" s="177" t="s">
+      <c r="B3" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="179"/>
-      <c r="K3" s="116">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="110"/>
+      <c r="K3" s="105">
         <v>1</v>
       </c>
-      <c r="L3" s="177" t="s">
+      <c r="L3" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="178"/>
-      <c r="N3" s="178"/>
-      <c r="O3" s="178"/>
-      <c r="P3" s="178"/>
-      <c r="Q3" s="178"/>
-      <c r="R3" s="178"/>
-      <c r="S3" s="179"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="109"/>
+      <c r="P3" s="109"/>
+      <c r="Q3" s="109"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="110"/>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
-      <c r="A4" s="117"/>
+      <c r="A4" s="106"/>
       <c r="B4" s="68" t="s">
         <v>44</v>
       </c>
@@ -6840,7 +6848,7 @@
       <c r="I4" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="117"/>
+      <c r="K4" s="106"/>
       <c r="L4" s="68" t="s">
         <v>44</v>
       </c>
@@ -6861,7 +6869,7 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1" thickBot="1">
-      <c r="A5" s="118"/>
+      <c r="A5" s="107"/>
       <c r="B5" s="70" t="s">
         <v>45</v>
       </c>
@@ -6878,7 +6886,7 @@
       <c r="I5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="118"/>
+      <c r="K5" s="107"/>
       <c r="L5" s="70" t="s">
         <v>45</v>
       </c>
@@ -6899,7 +6907,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
-      <c r="A6" s="106">
+      <c r="A6" s="146">
         <v>2</v>
       </c>
       <c r="B6" s="64" t="s">
@@ -6912,7 +6920,7 @@
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
       <c r="I6" s="65"/>
-      <c r="K6" s="106">
+      <c r="K6" s="146">
         <v>2</v>
       </c>
       <c r="L6" s="64" t="s">
@@ -6927,7 +6935,7 @@
       <c r="S6" s="65"/>
     </row>
     <row r="7" spans="1:19" ht="32.25" customHeight="1">
-      <c r="A7" s="106"/>
+      <c r="A7" s="146"/>
       <c r="B7" s="68" t="s">
         <v>48</v>
       </c>
@@ -6935,16 +6943,16 @@
       <c r="D7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="169" t="s">
+      <c r="E7" s="147" t="s">
         <v>88</v>
       </c>
-      <c r="F7" s="169"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="169"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
       <c r="I7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="106"/>
+      <c r="K7" s="146"/>
       <c r="L7" s="68" t="s">
         <v>48</v>
       </c>
@@ -6952,19 +6960,19 @@
       <c r="N7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="169" t="str">
+      <c r="O7" s="147" t="str">
         <f>E7</f>
         <v>7月10日至7月14日</v>
       </c>
-      <c r="P7" s="169"/>
-      <c r="Q7" s="169"/>
-      <c r="R7" s="169"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
+      <c r="R7" s="147"/>
       <c r="S7" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="37.5" customHeight="1">
-      <c r="A8" s="106"/>
+      <c r="A8" s="146"/>
       <c r="B8" s="68" t="s">
         <v>51</v>
       </c>
@@ -6977,7 +6985,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
       <c r="I8" s="5"/>
-      <c r="K8" s="106"/>
+      <c r="K8" s="146"/>
       <c r="L8" s="68" t="s">
         <v>51</v>
       </c>
@@ -6993,44 +7001,44 @@
       <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" ht="25" customHeight="1">
-      <c r="A9" s="106"/>
+      <c r="A9" s="146"/>
       <c r="B9" s="68"/>
-      <c r="C9" s="170" t="s">
+      <c r="C9" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
+      <c r="D9" s="114"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="114"/>
       <c r="G9" s="55"/>
-      <c r="H9" s="107" t="s">
+      <c r="H9" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="108"/>
-      <c r="K9" s="106"/>
+      <c r="I9" s="150"/>
+      <c r="K9" s="146"/>
       <c r="L9" s="68"/>
-      <c r="M9" s="170" t="s">
+      <c r="M9" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="112"/>
-      <c r="O9" s="112"/>
-      <c r="P9" s="112"/>
+      <c r="N9" s="114"/>
+      <c r="O9" s="114"/>
+      <c r="P9" s="114"/>
       <c r="Q9" s="55"/>
-      <c r="R9" s="107" t="s">
+      <c r="R9" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="S9" s="108"/>
+      <c r="S9" s="150"/>
     </row>
     <row r="10" spans="1:19" ht="25" customHeight="1">
-      <c r="A10" s="106"/>
+      <c r="A10" s="146"/>
       <c r="B10" s="56"/>
-      <c r="C10" s="109" t="s">
+      <c r="C10" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111" t="s">
+      <c r="D10" s="112"/>
+      <c r="E10" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="112"/>
+      <c r="F10" s="114"/>
       <c r="G10" s="55"/>
       <c r="H10" s="57" t="s">
         <v>23</v>
@@ -7038,16 +7046,16 @@
       <c r="I10" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="106"/>
+      <c r="K10" s="146"/>
       <c r="L10" s="56"/>
-      <c r="M10" s="109" t="s">
+      <c r="M10" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="110"/>
-      <c r="O10" s="111" t="s">
+      <c r="N10" s="112"/>
+      <c r="O10" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="P10" s="112"/>
+      <c r="P10" s="114"/>
       <c r="Q10" s="55"/>
       <c r="R10" s="57" t="s">
         <v>23</v>
@@ -7057,47 +7065,47 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="28" customHeight="1">
-      <c r="A11" s="106"/>
-      <c r="B11" s="130">
+      <c r="A11" s="146"/>
+      <c r="B11" s="115">
         <v>1</v>
       </c>
-      <c r="C11" s="133" t="s">
+      <c r="C11" s="118" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="134"/>
-      <c r="E11" s="155" t="s">
+      <c r="D11" s="136"/>
+      <c r="E11" s="124" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="140"/>
+      <c r="F11" s="125"/>
       <c r="G11" s="59"/>
-      <c r="H11" s="145" t="s">
+      <c r="H11" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="I11" s="151" t="s">
+      <c r="I11" s="133" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="106"/>
-      <c r="L11" s="130">
+      <c r="K11" s="146"/>
+      <c r="L11" s="115">
         <v>1</v>
       </c>
-      <c r="M11" s="133" t="str">
+      <c r="M11" s="118" t="str">
         <f>C11</f>
         <v xml:space="preserve">2025 年7月 10 日    </v>
       </c>
-      <c r="N11" s="134"/>
-      <c r="O11" s="155" t="str">
+      <c r="N11" s="136"/>
+      <c r="O11" s="124" t="str">
         <f>E11</f>
         <v>09:30-13:30(4H)
 14:30-17:00(2H30M)
 6H30M</v>
       </c>
-      <c r="P11" s="159"/>
+      <c r="P11" s="141"/>
       <c r="Q11" s="59"/>
-      <c r="R11" s="145" t="str">
+      <c r="R11" s="130" t="str">
         <f>H11</f>
         <v xml:space="preserve">     2025 年7月 10 日    </v>
       </c>
-      <c r="S11" s="151" t="str">
+      <c r="S11" s="133" t="str">
         <f>I11</f>
         <v>0950-1330(3H40m)
 1400-1715(3H10m)
@@ -7105,87 +7113,87 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="28" customHeight="1">
-      <c r="A12" s="106"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="142"/>
+      <c r="A12" s="146"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="138"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="127"/>
       <c r="G12" s="61"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="149"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="131"/>
-      <c r="M12" s="135"/>
-      <c r="N12" s="136"/>
-      <c r="O12" s="160"/>
-      <c r="P12" s="161"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="134"/>
+      <c r="K12" s="146"/>
+      <c r="L12" s="116"/>
+      <c r="M12" s="137"/>
+      <c r="N12" s="138"/>
+      <c r="O12" s="142"/>
+      <c r="P12" s="143"/>
       <c r="Q12" s="61"/>
-      <c r="R12" s="146"/>
-      <c r="S12" s="152"/>
+      <c r="R12" s="131"/>
+      <c r="S12" s="151"/>
     </row>
     <row r="13" spans="1:19" ht="28" customHeight="1">
-      <c r="A13" s="106"/>
-      <c r="B13" s="154"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="138"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="157"/>
+      <c r="A13" s="146"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="139"/>
+      <c r="D13" s="140"/>
+      <c r="E13" s="128"/>
+      <c r="F13" s="129"/>
       <c r="G13" s="60"/>
-      <c r="H13" s="147"/>
-      <c r="I13" s="158"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="154"/>
-      <c r="M13" s="137"/>
-      <c r="N13" s="138"/>
-      <c r="O13" s="162"/>
-      <c r="P13" s="163"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="135"/>
+      <c r="K13" s="146"/>
+      <c r="L13" s="117"/>
+      <c r="M13" s="139"/>
+      <c r="N13" s="140"/>
+      <c r="O13" s="144"/>
+      <c r="P13" s="145"/>
       <c r="Q13" s="60"/>
-      <c r="R13" s="147"/>
-      <c r="S13" s="153"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="152"/>
     </row>
     <row r="14" spans="1:19" ht="28" customHeight="1">
-      <c r="A14" s="106"/>
-      <c r="B14" s="130">
+      <c r="A14" s="146"/>
+      <c r="B14" s="115">
         <v>2</v>
       </c>
-      <c r="C14" s="133" t="s">
+      <c r="C14" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="134"/>
-      <c r="E14" s="155" t="s">
+      <c r="D14" s="136"/>
+      <c r="E14" s="124" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="140"/>
+      <c r="F14" s="125"/>
       <c r="G14" s="59"/>
-      <c r="H14" s="145" t="s">
+      <c r="H14" s="130" t="s">
         <v>94</v>
       </c>
-      <c r="I14" s="151" t="s">
+      <c r="I14" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="K14" s="106"/>
-      <c r="L14" s="130">
+      <c r="K14" s="146"/>
+      <c r="L14" s="115">
         <v>2</v>
       </c>
-      <c r="M14" s="133" t="str">
+      <c r="M14" s="118" t="str">
         <f>C14</f>
         <v xml:space="preserve">2025年 7 月  14 日    </v>
       </c>
-      <c r="N14" s="134"/>
-      <c r="O14" s="155" t="str">
+      <c r="N14" s="136"/>
+      <c r="O14" s="124" t="str">
         <f>E14</f>
         <v>09:30-13:30(4H)
 14:30-18:00(3H30M)
 7H30M</v>
       </c>
-      <c r="P14" s="159"/>
+      <c r="P14" s="141"/>
       <c r="Q14" s="59"/>
-      <c r="R14" s="145" t="str">
+      <c r="R14" s="130" t="str">
         <f>H14</f>
         <v xml:space="preserve">2025年 7 月  14 日        </v>
       </c>
-      <c r="S14" s="151" t="str">
+      <c r="S14" s="133" t="str">
         <f>I14</f>
         <v>0930-1330(4H)
 18:00-21:10(3H10M)
@@ -7193,238 +7201,238 @@
       </c>
     </row>
     <row r="15" spans="1:19" ht="28" customHeight="1">
-      <c r="A15" s="106"/>
-      <c r="B15" s="131"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="142"/>
+      <c r="A15" s="146"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="127"/>
       <c r="G15" s="61"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="149"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="131"/>
-      <c r="M15" s="135"/>
-      <c r="N15" s="136"/>
-      <c r="O15" s="160"/>
-      <c r="P15" s="161"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="134"/>
+      <c r="K15" s="146"/>
+      <c r="L15" s="116"/>
+      <c r="M15" s="137"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="142"/>
+      <c r="P15" s="143"/>
       <c r="Q15" s="61"/>
-      <c r="R15" s="146"/>
-      <c r="S15" s="152"/>
+      <c r="R15" s="131"/>
+      <c r="S15" s="151"/>
     </row>
     <row r="16" spans="1:19" ht="28" customHeight="1">
-      <c r="A16" s="106"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="137"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="156"/>
-      <c r="F16" s="157"/>
+      <c r="A16" s="146"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="139"/>
+      <c r="D16" s="140"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="129"/>
       <c r="G16" s="60"/>
-      <c r="H16" s="147"/>
-      <c r="I16" s="158"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="154"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="138"/>
-      <c r="O16" s="162"/>
-      <c r="P16" s="163"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="135"/>
+      <c r="K16" s="146"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="139"/>
+      <c r="N16" s="140"/>
+      <c r="O16" s="144"/>
+      <c r="P16" s="145"/>
       <c r="Q16" s="60"/>
-      <c r="R16" s="147"/>
-      <c r="S16" s="153"/>
+      <c r="R16" s="132"/>
+      <c r="S16" s="152"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1">
-      <c r="A17" s="106"/>
-      <c r="B17" s="130">
+      <c r="A17" s="146"/>
+      <c r="B17" s="115">
         <v>3</v>
       </c>
-      <c r="C17" s="133" t="s">
+      <c r="C17" s="118" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="134"/>
-      <c r="E17" s="139"/>
-      <c r="F17" s="140"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="154"/>
+      <c r="F17" s="125"/>
       <c r="G17" s="59"/>
-      <c r="H17" s="145" t="s">
+      <c r="H17" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="148"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="130">
+      <c r="I17" s="163"/>
+      <c r="K17" s="146"/>
+      <c r="L17" s="115">
         <v>3</v>
       </c>
-      <c r="M17" s="133" t="s">
+      <c r="M17" s="118" t="s">
         <v>73</v>
       </c>
-      <c r="N17" s="134"/>
-      <c r="O17" s="139"/>
-      <c r="P17" s="140"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="154"/>
+      <c r="P17" s="125"/>
       <c r="Q17" s="59"/>
-      <c r="R17" s="145" t="s">
+      <c r="R17" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="S17" s="148"/>
+      <c r="S17" s="163"/>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1">
-      <c r="A18" s="106"/>
-      <c r="B18" s="131"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="136"/>
-      <c r="E18" s="141"/>
-      <c r="F18" s="142"/>
+      <c r="A18" s="146"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="138"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="127"/>
       <c r="G18" s="61"/>
-      <c r="H18" s="146"/>
-      <c r="I18" s="149"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="131"/>
-      <c r="M18" s="135"/>
-      <c r="N18" s="136"/>
-      <c r="O18" s="141"/>
-      <c r="P18" s="142"/>
+      <c r="H18" s="131"/>
+      <c r="I18" s="134"/>
+      <c r="K18" s="146"/>
+      <c r="L18" s="116"/>
+      <c r="M18" s="137"/>
+      <c r="N18" s="138"/>
+      <c r="O18" s="126"/>
+      <c r="P18" s="127"/>
       <c r="Q18" s="61"/>
-      <c r="R18" s="146"/>
-      <c r="S18" s="149"/>
+      <c r="R18" s="131"/>
+      <c r="S18" s="134"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" thickBot="1">
-      <c r="A19" s="106"/>
-      <c r="B19" s="132"/>
-      <c r="C19" s="137"/>
-      <c r="D19" s="138"/>
-      <c r="E19" s="143"/>
-      <c r="F19" s="144"/>
+      <c r="A19" s="146"/>
+      <c r="B19" s="153"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="156"/>
       <c r="G19" s="62"/>
-      <c r="H19" s="147"/>
-      <c r="I19" s="150"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="132"/>
-      <c r="M19" s="137"/>
-      <c r="N19" s="138"/>
-      <c r="O19" s="143"/>
-      <c r="P19" s="144"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="157"/>
+      <c r="K19" s="146"/>
+      <c r="L19" s="153"/>
+      <c r="M19" s="139"/>
+      <c r="N19" s="140"/>
+      <c r="O19" s="155"/>
+      <c r="P19" s="156"/>
       <c r="Q19" s="62"/>
-      <c r="R19" s="147"/>
-      <c r="S19" s="150"/>
+      <c r="R19" s="132"/>
+      <c r="S19" s="157"/>
     </row>
     <row r="20" spans="1:20" ht="20.25" customHeight="1">
-      <c r="A20" s="116">
+      <c r="A20" s="105">
         <v>3</v>
       </c>
-      <c r="B20" s="119" t="s">
+      <c r="B20" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="121"/>
-      <c r="K20" s="116">
+      <c r="C20" s="178"/>
+      <c r="D20" s="178"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="178"/>
+      <c r="G20" s="178"/>
+      <c r="H20" s="178"/>
+      <c r="I20" s="179"/>
+      <c r="K20" s="105">
         <v>3</v>
       </c>
-      <c r="L20" s="119" t="s">
+      <c r="L20" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="M20" s="120"/>
-      <c r="N20" s="120"/>
-      <c r="O20" s="120"/>
-      <c r="P20" s="120"/>
-      <c r="Q20" s="120"/>
-      <c r="R20" s="120"/>
-      <c r="S20" s="121"/>
+      <c r="M20" s="178"/>
+      <c r="N20" s="178"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="178"/>
+      <c r="Q20" s="178"/>
+      <c r="R20" s="178"/>
+      <c r="S20" s="179"/>
     </row>
     <row r="21" spans="1:20" ht="45" customHeight="1">
-      <c r="A21" s="117"/>
-      <c r="B21" s="122" t="s">
+      <c r="A21" s="106"/>
+      <c r="B21" s="164" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="123"/>
-      <c r="D21" s="101" t="s">
+      <c r="C21" s="165"/>
+      <c r="D21" s="169" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="102"/>
-      <c r="F21" s="103" t="s">
+      <c r="E21" s="170"/>
+      <c r="F21" s="171" t="s">
         <v>57</v>
       </c>
-      <c r="G21" s="104"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="105"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="122" t="s">
+      <c r="G21" s="172"/>
+      <c r="H21" s="172"/>
+      <c r="I21" s="173"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="164" t="s">
         <v>61</v>
       </c>
-      <c r="M21" s="123"/>
-      <c r="N21" s="101" t="s">
+      <c r="M21" s="165"/>
+      <c r="N21" s="169" t="s">
         <v>62</v>
       </c>
-      <c r="O21" s="102"/>
-      <c r="P21" s="103" t="s">
+      <c r="O21" s="170"/>
+      <c r="P21" s="171" t="s">
         <v>57</v>
       </c>
-      <c r="Q21" s="104"/>
-      <c r="R21" s="104"/>
-      <c r="S21" s="105"/>
+      <c r="Q21" s="172"/>
+      <c r="R21" s="172"/>
+      <c r="S21" s="173"/>
     </row>
     <row r="22" spans="1:20" ht="63.75" customHeight="1">
-      <c r="A22" s="117"/>
+      <c r="A22" s="106"/>
       <c r="B22" s="73"/>
       <c r="C22" s="60"/>
       <c r="D22" s="74"/>
       <c r="E22" s="60"/>
-      <c r="F22" s="113" t="s">
+      <c r="F22" s="174" t="s">
         <v>66</v>
       </c>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="115"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="175"/>
+      <c r="I22" s="176"/>
       <c r="J22" s="86"/>
-      <c r="K22" s="117"/>
+      <c r="K22" s="106"/>
       <c r="L22" s="73"/>
       <c r="M22" s="60"/>
       <c r="N22" s="74"/>
       <c r="O22" s="60"/>
-      <c r="P22" s="113" t="s">
+      <c r="P22" s="174" t="s">
         <v>65</v>
       </c>
-      <c r="Q22" s="114"/>
-      <c r="R22" s="114"/>
-      <c r="S22" s="115"/>
+      <c r="Q22" s="175"/>
+      <c r="R22" s="175"/>
+      <c r="S22" s="176"/>
       <c r="T22" s="85"/>
     </row>
     <row r="23" spans="1:20" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A23" s="118"/>
-      <c r="B23" s="124" t="s">
+      <c r="A23" s="107"/>
+      <c r="B23" s="166" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="125"/>
-      <c r="D23" s="126" t="s">
+      <c r="C23" s="159"/>
+      <c r="D23" s="158" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="125"/>
-      <c r="F23" s="127" t="s">
+      <c r="E23" s="159"/>
+      <c r="F23" s="160" t="s">
         <v>54</v>
       </c>
-      <c r="G23" s="128"/>
-      <c r="H23" s="126" t="s">
+      <c r="G23" s="161"/>
+      <c r="H23" s="158" t="s">
         <v>77</v>
       </c>
-      <c r="I23" s="129"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="124" t="s">
+      <c r="I23" s="162"/>
+      <c r="K23" s="107"/>
+      <c r="L23" s="166" t="s">
         <v>76</v>
       </c>
-      <c r="M23" s="125"/>
-      <c r="N23" s="126" t="s">
+      <c r="M23" s="159"/>
+      <c r="N23" s="158" t="s">
         <v>74</v>
       </c>
-      <c r="O23" s="125"/>
-      <c r="P23" s="127" t="s">
+      <c r="O23" s="159"/>
+      <c r="P23" s="160" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" s="128"/>
-      <c r="R23" s="126" t="s">
+      <c r="Q23" s="161"/>
+      <c r="R23" s="158" t="s">
         <v>75</v>
       </c>
-      <c r="S23" s="129"/>
+      <c r="S23" s="162"/>
     </row>
     <row r="24" spans="1:20" ht="31.5" customHeight="1">
       <c r="A24" s="67" t="s">
@@ -7453,7 +7461,7 @@
       <c r="P24" s="72"/>
       <c r="Q24" s="72"/>
       <c r="R24" s="72"/>
-      <c r="S24" s="99" t="s">
+      <c r="S24" s="167" t="s">
         <v>53</v>
       </c>
       <c r="T24" s="84"/>
@@ -7476,16 +7484,61 @@
       <c r="P25" s="70"/>
       <c r="Q25" s="70"/>
       <c r="R25" s="70"/>
-      <c r="S25" s="100"/>
+      <c r="S25" s="168"/>
       <c r="T25" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="S24:S25"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="A6:A19"/>
+    <mergeCell ref="K6:K19"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="M9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:D13"/>
+    <mergeCell ref="E11:F13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:D16"/>
+    <mergeCell ref="E14:F16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:N16"/>
+    <mergeCell ref="O14:P16"/>
+    <mergeCell ref="R14:R16"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="M11:N13"/>
+    <mergeCell ref="O11:P13"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="E17:F19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="L17:L19"/>
+    <mergeCell ref="M17:N19"/>
+    <mergeCell ref="O17:P19"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="K20:K23"/>
@@ -7502,56 +7555,11 @@
     <mergeCell ref="N23:O23"/>
     <mergeCell ref="P23:Q23"/>
     <mergeCell ref="R23:S23"/>
-    <mergeCell ref="L17:L19"/>
-    <mergeCell ref="M17:N19"/>
-    <mergeCell ref="O17:P19"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="E17:F19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:D16"/>
-    <mergeCell ref="E14:F16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:N16"/>
-    <mergeCell ref="O14:P16"/>
-    <mergeCell ref="R14:R16"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="M11:N13"/>
-    <mergeCell ref="O11:P13"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="A6:A19"/>
-    <mergeCell ref="K6:K19"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="M9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:D13"/>
-    <mergeCell ref="E11:F13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="P22:S22"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -7592,83 +7600,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="184.5" customHeight="1">
-      <c r="A1" s="230" t="s">
+      <c r="A1" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="231"/>
-      <c r="C1" s="231"/>
-      <c r="D1" s="231"/>
-      <c r="E1" s="231"/>
-      <c r="F1" s="231"/>
-      <c r="G1" s="231"/>
-      <c r="H1" s="231"/>
-      <c r="I1" s="232"/>
-      <c r="K1" s="230" t="s">
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="182"/>
+      <c r="K1" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="231"/>
-      <c r="M1" s="231"/>
-      <c r="N1" s="231"/>
-      <c r="O1" s="231"/>
-      <c r="P1" s="231"/>
-      <c r="Q1" s="231"/>
-      <c r="R1" s="231"/>
-      <c r="S1" s="232"/>
+      <c r="L1" s="181"/>
+      <c r="M1" s="181"/>
+      <c r="N1" s="181"/>
+      <c r="O1" s="181"/>
+      <c r="P1" s="181"/>
+      <c r="Q1" s="181"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="182"/>
     </row>
     <row r="2" spans="1:19" ht="139.5" customHeight="1" thickBot="1">
-      <c r="A2" s="233" t="s">
+      <c r="A2" s="183" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="234"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="234"/>
-      <c r="H2" s="234"/>
-      <c r="I2" s="235"/>
-      <c r="K2" s="233" t="s">
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="185"/>
+      <c r="K2" s="183" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="234"/>
-      <c r="M2" s="234"/>
-      <c r="N2" s="234"/>
-      <c r="O2" s="234"/>
-      <c r="P2" s="234"/>
-      <c r="Q2" s="234"/>
-      <c r="R2" s="234"/>
-      <c r="S2" s="235"/>
+      <c r="L2" s="184"/>
+      <c r="M2" s="184"/>
+      <c r="N2" s="184"/>
+      <c r="O2" s="184"/>
+      <c r="P2" s="184"/>
+      <c r="Q2" s="184"/>
+      <c r="R2" s="184"/>
+      <c r="S2" s="185"/>
     </row>
     <row r="3" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A3" s="180">
+      <c r="A3" s="186">
         <v>1</v>
       </c>
-      <c r="B3" s="237" t="s">
+      <c r="B3" s="189" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="238"/>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="238"/>
-      <c r="I3" s="239"/>
-      <c r="K3" s="180">
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+      <c r="I3" s="191"/>
+      <c r="K3" s="186">
         <v>1</v>
       </c>
-      <c r="L3" s="237" t="s">
+      <c r="L3" s="189" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="238"/>
-      <c r="N3" s="238"/>
-      <c r="O3" s="238"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="239"/>
+      <c r="M3" s="190"/>
+      <c r="N3" s="190"/>
+      <c r="O3" s="190"/>
+      <c r="P3" s="190"/>
+      <c r="Q3" s="190"/>
+      <c r="R3" s="190"/>
+      <c r="S3" s="191"/>
     </row>
     <row r="4" spans="1:19" s="12" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A4" s="181"/>
+      <c r="A4" s="187"/>
       <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
@@ -7685,7 +7693,7 @@
         <v>79</v>
       </c>
       <c r="I4" s="11"/>
-      <c r="K4" s="181"/>
+      <c r="K4" s="187"/>
       <c r="L4" s="8" t="s">
         <v>19</v>
       </c>
@@ -7704,7 +7712,7 @@
       <c r="S4" s="11"/>
     </row>
     <row r="5" spans="1:19" s="12" customFormat="1" ht="222" customHeight="1" thickBot="1">
-      <c r="A5" s="236"/>
+      <c r="A5" s="188"/>
       <c r="B5" s="13" t="s">
         <v>17</v>
       </c>
@@ -7721,7 +7729,7 @@
         <v>80</v>
       </c>
       <c r="I5" s="16"/>
-      <c r="K5" s="236"/>
+      <c r="K5" s="188"/>
       <c r="L5" s="13" t="s">
         <v>17</v>
       </c>
@@ -7740,7 +7748,7 @@
       <c r="S5" s="16"/>
     </row>
     <row r="6" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A6" s="204">
+      <c r="A6" s="223">
         <v>2</v>
       </c>
       <c r="B6" s="17" t="s">
@@ -7753,7 +7761,7 @@
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
       <c r="I6" s="19"/>
-      <c r="K6" s="204">
+      <c r="K6" s="223">
         <v>2</v>
       </c>
       <c r="L6" s="17" t="s">
@@ -7768,26 +7776,26 @@
       <c r="S6" s="19"/>
     </row>
     <row r="7" spans="1:19" s="12" customFormat="1" ht="207" customHeight="1">
-      <c r="A7" s="205"/>
-      <c r="B7" s="214" t="s">
+      <c r="A7" s="224"/>
+      <c r="B7" s="227" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="215"/>
-      <c r="D7" s="215"/>
-      <c r="E7" s="215"/>
+      <c r="C7" s="228"/>
+      <c r="D7" s="228"/>
+      <c r="E7" s="228"/>
       <c r="F7" s="90"/>
       <c r="G7" s="240" t="s">
         <v>98</v>
       </c>
       <c r="H7" s="240"/>
       <c r="I7" s="241"/>
-      <c r="K7" s="205"/>
-      <c r="L7" s="214" t="s">
+      <c r="K7" s="224"/>
+      <c r="L7" s="227" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="215"/>
-      <c r="N7" s="215"/>
-      <c r="O7" s="215"/>
+      <c r="M7" s="228"/>
+      <c r="N7" s="228"/>
+      <c r="O7" s="228"/>
       <c r="P7" s="90"/>
       <c r="Q7" s="240" t="str">
         <f>G7</f>
@@ -7797,7 +7805,7 @@
       <c r="S7" s="241"/>
     </row>
     <row r="8" spans="1:19" s="12" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A8" s="205"/>
+      <c r="A8" s="224"/>
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
@@ -7814,7 +7822,7 @@
         <v>36</v>
       </c>
       <c r="I8" s="11"/>
-      <c r="K8" s="205"/>
+      <c r="K8" s="224"/>
       <c r="L8" s="8" t="s">
         <v>13</v>
       </c>
@@ -7835,7 +7843,7 @@
       <c r="S8" s="11"/>
     </row>
     <row r="9" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A9" s="205"/>
+      <c r="A9" s="224"/>
       <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
@@ -7852,7 +7860,7 @@
       <c r="I9" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="205"/>
+      <c r="K9" s="224"/>
       <c r="L9" s="8" t="s">
         <v>12</v>
       </c>
@@ -7871,7 +7879,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A10" s="205"/>
+      <c r="A10" s="224"/>
       <c r="B10" s="28" t="s">
         <v>8</v>
       </c>
@@ -7890,7 +7898,7 @@
       <c r="I10" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="K10" s="205"/>
+      <c r="K10" s="224"/>
       <c r="L10" s="28" t="s">
         <v>8</v>
       </c>
@@ -7914,8 +7922,8 @@
       </c>
     </row>
     <row r="11" spans="1:19" s="27" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A11" s="205"/>
-      <c r="B11" s="198" t="s">
+      <c r="A11" s="224"/>
+      <c r="B11" s="217" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="34" t="s">
@@ -7933,8 +7941,8 @@
       <c r="I11" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="K11" s="205"/>
-      <c r="L11" s="198" t="s">
+      <c r="K11" s="224"/>
+      <c r="L11" s="217" t="s">
         <v>7</v>
       </c>
       <c r="M11" s="34" t="s">
@@ -7957,8 +7965,8 @@
       </c>
     </row>
     <row r="12" spans="1:19" s="27" customFormat="1" ht="147" customHeight="1">
-      <c r="A12" s="205"/>
-      <c r="B12" s="199"/>
+      <c r="A12" s="224"/>
+      <c r="B12" s="218"/>
       <c r="C12" s="34" t="s">
         <v>30</v>
       </c>
@@ -7968,8 +7976,8 @@
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
       <c r="I12" s="33"/>
-      <c r="K12" s="205"/>
-      <c r="L12" s="199"/>
+      <c r="K12" s="224"/>
+      <c r="L12" s="218"/>
       <c r="M12" s="34" t="s">
         <v>30</v>
       </c>
@@ -7981,60 +7989,60 @@
       <c r="S12" s="33"/>
     </row>
     <row r="13" spans="1:19" s="27" customFormat="1" ht="154.5" customHeight="1">
-      <c r="A13" s="205"/>
-      <c r="B13" s="200"/>
-      <c r="C13" s="201" t="s">
+      <c r="A13" s="224"/>
+      <c r="B13" s="219"/>
+      <c r="C13" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="202"/>
-      <c r="E13" s="202"/>
-      <c r="F13" s="203"/>
+      <c r="D13" s="221"/>
+      <c r="E13" s="221"/>
+      <c r="F13" s="222"/>
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
       <c r="I13" s="33"/>
-      <c r="K13" s="205"/>
-      <c r="L13" s="200"/>
-      <c r="M13" s="201" t="s">
+      <c r="K13" s="224"/>
+      <c r="L13" s="219"/>
+      <c r="M13" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="N13" s="202"/>
-      <c r="O13" s="202"/>
-      <c r="P13" s="203"/>
+      <c r="N13" s="221"/>
+      <c r="O13" s="221"/>
+      <c r="P13" s="222"/>
       <c r="Q13" s="32"/>
       <c r="R13" s="32"/>
       <c r="S13" s="33"/>
     </row>
     <row r="14" spans="1:19" s="27" customFormat="1" ht="219.75" customHeight="1">
-      <c r="A14" s="205"/>
-      <c r="B14" s="198" t="s">
+      <c r="A14" s="224"/>
+      <c r="B14" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="211" t="s">
+      <c r="C14" s="202" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-      <c r="F14" s="213"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="204"/>
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
       <c r="I14" s="33"/>
-      <c r="K14" s="205"/>
-      <c r="L14" s="198" t="s">
+      <c r="K14" s="224"/>
+      <c r="L14" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="211" t="s">
+      <c r="M14" s="202" t="s">
         <v>68</v>
       </c>
-      <c r="N14" s="212"/>
-      <c r="O14" s="212"/>
-      <c r="P14" s="213"/>
+      <c r="N14" s="203"/>
+      <c r="O14" s="203"/>
+      <c r="P14" s="204"/>
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="33"/>
     </row>
     <row r="15" spans="1:19" s="27" customFormat="1" ht="157.5" customHeight="1">
-      <c r="A15" s="205"/>
-      <c r="B15" s="199"/>
+      <c r="A15" s="224"/>
+      <c r="B15" s="218"/>
       <c r="C15" s="34" t="s">
         <v>31</v>
       </c>
@@ -8044,8 +8052,8 @@
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
-      <c r="K15" s="205"/>
-      <c r="L15" s="199"/>
+      <c r="K15" s="224"/>
+      <c r="L15" s="218"/>
       <c r="M15" s="34" t="s">
         <v>31</v>
       </c>
@@ -8057,8 +8065,8 @@
       <c r="S15" s="33"/>
     </row>
     <row r="16" spans="1:19" s="27" customFormat="1" ht="120" customHeight="1">
-      <c r="A16" s="205"/>
-      <c r="B16" s="199"/>
+      <c r="A16" s="224"/>
+      <c r="B16" s="218"/>
       <c r="C16" s="34" t="s">
         <v>32</v>
       </c>
@@ -8068,8 +8076,8 @@
       <c r="G16" s="38"/>
       <c r="H16" s="77"/>
       <c r="I16" s="78"/>
-      <c r="K16" s="205"/>
-      <c r="L16" s="199"/>
+      <c r="K16" s="224"/>
+      <c r="L16" s="218"/>
       <c r="M16" s="34" t="s">
         <v>32</v>
       </c>
@@ -8081,8 +8089,8 @@
       <c r="S16" s="78"/>
     </row>
     <row r="17" spans="1:19" s="27" customFormat="1" ht="112.5" customHeight="1">
-      <c r="A17" s="205"/>
-      <c r="B17" s="199"/>
+      <c r="A17" s="224"/>
+      <c r="B17" s="218"/>
       <c r="C17" s="34" t="s">
         <v>37</v>
       </c>
@@ -8092,8 +8100,8 @@
       <c r="G17" s="38"/>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="K17" s="205"/>
-      <c r="L17" s="199"/>
+      <c r="K17" s="224"/>
+      <c r="L17" s="218"/>
       <c r="M17" s="34" t="s">
         <v>37</v>
       </c>
@@ -8105,32 +8113,32 @@
       <c r="S17" s="40"/>
     </row>
     <row r="18" spans="1:19" s="27" customFormat="1" ht="165" customHeight="1">
-      <c r="A18" s="205"/>
-      <c r="B18" s="199"/>
-      <c r="C18" s="208" t="s">
+      <c r="A18" s="224"/>
+      <c r="B18" s="218"/>
+      <c r="C18" s="199" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="209"/>
-      <c r="E18" s="209"/>
-      <c r="F18" s="210"/>
+      <c r="D18" s="200"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="201"/>
       <c r="G18" s="41"/>
       <c r="H18" s="41"/>
       <c r="I18" s="42"/>
-      <c r="K18" s="205"/>
-      <c r="L18" s="199"/>
-      <c r="M18" s="208" t="s">
+      <c r="K18" s="224"/>
+      <c r="L18" s="218"/>
+      <c r="M18" s="199" t="s">
         <v>38</v>
       </c>
-      <c r="N18" s="209"/>
-      <c r="O18" s="209"/>
-      <c r="P18" s="210"/>
+      <c r="N18" s="200"/>
+      <c r="O18" s="200"/>
+      <c r="P18" s="201"/>
       <c r="Q18" s="41"/>
       <c r="R18" s="41"/>
       <c r="S18" s="42"/>
     </row>
     <row r="19" spans="1:19" s="27" customFormat="1" ht="157.5" customHeight="1">
-      <c r="A19" s="205"/>
-      <c r="B19" s="199"/>
+      <c r="A19" s="224"/>
+      <c r="B19" s="218"/>
       <c r="C19" s="43" t="s">
         <v>4</v>
       </c>
@@ -8140,8 +8148,8 @@
       <c r="G19" s="44"/>
       <c r="H19" s="44"/>
       <c r="I19" s="40"/>
-      <c r="K19" s="205"/>
-      <c r="L19" s="199"/>
+      <c r="K19" s="224"/>
+      <c r="L19" s="218"/>
       <c r="M19" s="43" t="s">
         <v>4</v>
       </c>
@@ -8153,8 +8161,8 @@
       <c r="S19" s="40"/>
     </row>
     <row r="20" spans="1:19" s="27" customFormat="1" ht="150" customHeight="1">
-      <c r="A20" s="205"/>
-      <c r="B20" s="199"/>
+      <c r="A20" s="224"/>
+      <c r="B20" s="218"/>
       <c r="C20" s="34" t="s">
         <v>33</v>
       </c>
@@ -8164,8 +8172,8 @@
       <c r="G20" s="45"/>
       <c r="H20" s="45"/>
       <c r="I20" s="46"/>
-      <c r="K20" s="205"/>
-      <c r="L20" s="199"/>
+      <c r="K20" s="224"/>
+      <c r="L20" s="218"/>
       <c r="M20" s="34" t="s">
         <v>33</v>
       </c>
@@ -8177,8 +8185,8 @@
       <c r="S20" s="46"/>
     </row>
     <row r="21" spans="1:19" s="27" customFormat="1" ht="127.5" customHeight="1" thickBot="1">
-      <c r="A21" s="206"/>
-      <c r="B21" s="207"/>
+      <c r="A21" s="225"/>
+      <c r="B21" s="226"/>
       <c r="C21" s="34" t="s">
         <v>34</v>
       </c>
@@ -8188,8 +8196,8 @@
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
       <c r="I21" s="47"/>
-      <c r="K21" s="206"/>
-      <c r="L21" s="207"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="226"/>
       <c r="M21" s="34" t="s">
         <v>34</v>
       </c>
@@ -8201,85 +8209,85 @@
       <c r="S21" s="47"/>
     </row>
     <row r="22" spans="1:19" s="7" customFormat="1" ht="132" customHeight="1">
-      <c r="A22" s="180">
+      <c r="A22" s="186">
         <v>3</v>
       </c>
-      <c r="B22" s="182" t="s">
+      <c r="B22" s="229" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="183"/>
-      <c r="D22" s="183"/>
-      <c r="E22" s="183"/>
-      <c r="F22" s="183"/>
-      <c r="G22" s="183"/>
-      <c r="H22" s="183"/>
-      <c r="I22" s="184"/>
-      <c r="K22" s="180">
+      <c r="C22" s="230"/>
+      <c r="D22" s="230"/>
+      <c r="E22" s="230"/>
+      <c r="F22" s="230"/>
+      <c r="G22" s="230"/>
+      <c r="H22" s="230"/>
+      <c r="I22" s="231"/>
+      <c r="K22" s="186">
         <v>3</v>
       </c>
-      <c r="L22" s="182" t="s">
+      <c r="L22" s="229" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="183"/>
-      <c r="N22" s="183"/>
-      <c r="O22" s="183"/>
-      <c r="P22" s="183"/>
-      <c r="Q22" s="183"/>
-      <c r="R22" s="183"/>
-      <c r="S22" s="184"/>
+      <c r="M22" s="230"/>
+      <c r="N22" s="230"/>
+      <c r="O22" s="230"/>
+      <c r="P22" s="230"/>
+      <c r="Q22" s="230"/>
+      <c r="R22" s="230"/>
+      <c r="S22" s="231"/>
     </row>
     <row r="23" spans="1:19" s="27" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A23" s="181"/>
-      <c r="B23" s="185" t="s">
+      <c r="A23" s="187"/>
+      <c r="B23" s="232" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="186"/>
-      <c r="D23" s="187" t="s">
+      <c r="C23" s="233"/>
+      <c r="D23" s="211" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="188"/>
-      <c r="F23" s="186"/>
-      <c r="G23" s="187" t="s">
+      <c r="E23" s="234"/>
+      <c r="F23" s="233"/>
+      <c r="G23" s="211" t="s">
         <v>55</v>
       </c>
-      <c r="H23" s="189"/>
+      <c r="H23" s="212"/>
       <c r="I23" s="48"/>
-      <c r="K23" s="181"/>
-      <c r="L23" s="185" t="s">
+      <c r="K23" s="187"/>
+      <c r="L23" s="232" t="s">
         <v>58</v>
       </c>
-      <c r="M23" s="186"/>
-      <c r="N23" s="187" t="s">
+      <c r="M23" s="233"/>
+      <c r="N23" s="211" t="s">
         <v>63</v>
       </c>
-      <c r="O23" s="188"/>
-      <c r="P23" s="186"/>
-      <c r="Q23" s="187" t="s">
+      <c r="O23" s="234"/>
+      <c r="P23" s="233"/>
+      <c r="Q23" s="211" t="s">
         <v>55</v>
       </c>
-      <c r="R23" s="189"/>
+      <c r="R23" s="212"/>
       <c r="S23" s="48"/>
     </row>
     <row r="24" spans="1:19" s="27" customFormat="1" ht="199.5" customHeight="1">
-      <c r="A24" s="181"/>
+      <c r="A24" s="187"/>
       <c r="B24" s="89"/>
       <c r="C24" s="88"/>
-      <c r="D24" s="195" t="s">
+      <c r="D24" s="237" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="196"/>
-      <c r="F24" s="197"/>
+      <c r="E24" s="238"/>
+      <c r="F24" s="239"/>
       <c r="G24" s="87"/>
       <c r="H24" s="49" t="s">
         <v>39</v>
       </c>
       <c r="I24" s="48"/>
-      <c r="K24" s="181"/>
+      <c r="K24" s="187"/>
       <c r="L24" s="89"/>
       <c r="M24" s="79"/>
-      <c r="N24" s="195"/>
-      <c r="O24" s="196"/>
-      <c r="P24" s="197"/>
+      <c r="N24" s="237"/>
+      <c r="O24" s="238"/>
+      <c r="P24" s="239"/>
       <c r="Q24" s="87"/>
       <c r="R24" s="49" t="s">
         <v>39</v>
@@ -8287,65 +8295,65 @@
       <c r="S24" s="48"/>
     </row>
     <row r="25" spans="1:19" s="27" customFormat="1" ht="124.5" customHeight="1">
-      <c r="A25" s="181"/>
+      <c r="A25" s="187"/>
       <c r="B25" s="80"/>
       <c r="C25" s="81"/>
       <c r="D25" s="82"/>
       <c r="E25" s="83"/>
       <c r="F25" s="81"/>
       <c r="G25" s="96"/>
-      <c r="H25" s="224" t="s">
+      <c r="H25" s="194" t="s">
         <v>67</v>
       </c>
-      <c r="I25" s="225"/>
-      <c r="K25" s="181"/>
+      <c r="I25" s="195"/>
+      <c r="K25" s="187"/>
       <c r="L25" s="51"/>
       <c r="M25" s="91"/>
       <c r="N25" s="82"/>
       <c r="O25" s="83"/>
       <c r="P25" s="81"/>
       <c r="Q25" s="96"/>
-      <c r="R25" s="224" t="s">
+      <c r="R25" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="S25" s="225"/>
+      <c r="S25" s="195"/>
     </row>
     <row r="26" spans="1:19" s="27" customFormat="1" ht="274.5" customHeight="1" thickBot="1">
-      <c r="A26" s="181"/>
-      <c r="B26" s="193" t="s">
+      <c r="A26" s="187"/>
+      <c r="B26" s="235" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="194"/>
-      <c r="D26" s="190" t="s">
+      <c r="C26" s="236"/>
+      <c r="D26" s="196" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="191"/>
-      <c r="F26" s="192"/>
+      <c r="E26" s="197"/>
+      <c r="F26" s="198"/>
       <c r="G26" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="226" t="s">
+      <c r="H26" s="213" t="s">
         <v>71</v>
       </c>
-      <c r="I26" s="227"/>
+      <c r="I26" s="214"/>
       <c r="J26" s="93"/>
-      <c r="K26" s="181"/>
-      <c r="L26" s="193" t="s">
+      <c r="K26" s="187"/>
+      <c r="L26" s="235" t="s">
         <v>69</v>
       </c>
-      <c r="M26" s="194"/>
-      <c r="N26" s="190" t="s">
+      <c r="M26" s="236"/>
+      <c r="N26" s="196" t="s">
         <v>70</v>
       </c>
-      <c r="O26" s="191"/>
-      <c r="P26" s="192"/>
+      <c r="O26" s="197"/>
+      <c r="P26" s="198"/>
       <c r="Q26" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="R26" s="228" t="s">
+      <c r="R26" s="215" t="s">
         <v>71</v>
       </c>
-      <c r="S26" s="229"/>
+      <c r="S26" s="216"/>
     </row>
     <row r="27" spans="1:19" s="7" customFormat="1" ht="200.15" customHeight="1">
       <c r="A27" s="50" t="s">
@@ -8369,10 +8377,10 @@
       <c r="O27" s="92"/>
       <c r="P27" s="92"/>
       <c r="Q27" s="92"/>
-      <c r="R27" s="218" t="s">
+      <c r="R27" s="205" t="s">
         <v>40</v>
       </c>
-      <c r="S27" s="219"/>
+      <c r="S27" s="206"/>
     </row>
     <row r="28" spans="1:19" s="27" customFormat="1" ht="106.5" customHeight="1">
       <c r="A28" s="51"/>
@@ -8384,8 +8392,8 @@
       <c r="M28" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="R28" s="220"/>
-      <c r="S28" s="221"/>
+      <c r="R28" s="207"/>
+      <c r="S28" s="208"/>
     </row>
     <row r="29" spans="1:19" ht="79.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A29" s="52"/>
@@ -8405,8 +8413,8 @@
       <c r="O29" s="53"/>
       <c r="P29" s="53"/>
       <c r="Q29" s="53"/>
-      <c r="R29" s="222"/>
-      <c r="S29" s="223"/>
+      <c r="R29" s="209"/>
+      <c r="S29" s="210"/>
     </row>
     <row r="50" spans="13:13">
       <c r="M50" s="94"/>
@@ -8416,29 +8424,14 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="R27:S29"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="K22:K26"/>
-    <mergeCell ref="L22:S22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:S3"/>
     <mergeCell ref="A6:A21"/>
     <mergeCell ref="K6:K21"/>
     <mergeCell ref="B7:E7"/>
@@ -8453,14 +8446,29 @@
     <mergeCell ref="M14:P14"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="M18:P18"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="K22:K26"/>
+    <mergeCell ref="L22:S22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R27:S29"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:P23"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
